--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -7401,7 +7401,7 @@
       </c>
       <c r="B2" s="52" t="inlineStr">
         <is>
-          <t>Item hardware: comma 3X with integrated panda, Toyota harness and relay box, installed in a 2020 Corolla LE</t>
+          <t>Item hardware: comma 3X with integrated panda, Toyota harness and relay box, installed in a Corolla E210 · ZRE212 · US (CFG-001)</t>
         </is>
       </c>
       <c r="C2" s="52" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -780,7 +780,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.3 · draft</t>
+          <t>0.4 · draft</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>RT-1</t>
+          <t>RT-2</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.3 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.4 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -252,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -372,6 +372,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -780,7 +781,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.4 · draft</t>
+          <t>0.5 · draft</t>
         </is>
       </c>
     </row>
@@ -858,7 +859,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -868,7 +869,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -878,7 +879,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -909,7 +910,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>13 (13)</t>
+          <t>14 (14)</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3812,7 +3813,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Intercept relay and relay driver</t>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
           </r>
         </is>
       </c>
@@ -3938,7 +3939,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay stays intercepting when commanded released</t>
+            <t>Intercept switch stays in intercept when released</t>
           </r>
         </is>
       </c>
@@ -3955,7 +3956,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay contacts welded in the intercept position</t>
+            <t>Analog switch U1 or U2 stuck in the intercept (NO) position, or its IN input damaged high</t>
           </r>
         </is>
       </c>
@@ -4036,30 +4037,30 @@
       <c r="S13" s="49" t="inlineStr"/>
     </row>
     <row r="14" ht="87" customHeight="1">
-      <c r="A14" s="50" t="n"/>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="50" t="n"/>
-      <c r="D14" s="50" t="n"/>
-      <c r="E14" s="50" t="n"/>
-      <c r="F14" s="50" t="n"/>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="A14" s="51" t="n"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="43" t="inlineStr">
         <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="H14" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay driver output (MCU pin or transistor) stuck on</t>
-          </r>
-        </is>
-      </c>
-      <c r="I14" s="34" t="inlineStr">
+      <c r="H14" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SBU1 drive stuck high (device-side driver or MCU pin, UK-06)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4080,10 +4081,10 @@
           </r>
         </is>
       </c>
-      <c r="J14" s="35" t="n">
+      <c r="J14" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="K14" s="34" t="inlineStr">
+      <c r="K14" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4095,15 +4096,15 @@
           </r>
         </is>
       </c>
-      <c r="L14" s="36" t="n">
+      <c r="L14" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M14" s="37" t="inlineStr">
+      <c r="M14" s="47" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N14" s="34" t="inlineStr">
+      <c r="N14" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4125,195 +4126,26 @@
           </r>
         </is>
       </c>
-      <c r="O14" s="38" t="inlineStr">
+      <c r="O14" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P14" s="33" t="inlineStr"/>
-      <c r="Q14" s="33" t="inlineStr"/>
-      <c r="R14" s="39" t="inlineStr"/>
-      <c r="S14" s="39" t="inlineStr"/>
+      <c r="P14" s="43" t="inlineStr"/>
+      <c r="Q14" s="43" t="inlineStr"/>
+      <c r="R14" s="49" t="inlineStr"/>
+      <c r="S14" s="49" t="inlineStr"/>
     </row>
-    <row r="15" ht="100.5" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Intercept relay and relay driver</t>
-          </r>
-        </is>
-      </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
-          </r>
-        </is>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Erratic or excessive steering or braking</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Conflicting steering and ACC commands</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock camera LKA/ACC messages reach the car together with panda TX</t>
-          </r>
-        </is>
-      </c>
-      <c r="D15" s="31" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-006</t>
-        </is>
-      </c>
-      <c r="E15" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-011 · stuck
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Relay stays released when commanded to intercept</t>
-          </r>
-        </is>
-      </c>
+    <row r="15" ht="181.5" customHeight="1">
+      <c r="A15" s="50" t="n"/>
+      <c r="B15" s="50" t="n"/>
+      <c r="C15" s="50" t="n"/>
+      <c r="D15" s="50" t="n"/>
+      <c r="E15" s="50" t="n"/>
+      <c r="F15" s="50" t="n"/>
       <c r="G15" s="33" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="H15" s="34" t="inlineStr">
@@ -4324,7 +4156,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Relay coil or driver open, or contacts welded in the stock position</t>
+            <t>Pull-down R2 or R3 open, so IN floats when the device stops driving SBU1 (reset, watchdog, hang, unplugged cable)</t>
           </r>
         </is>
       </c>
@@ -4360,21 +4192,12 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• Relay-malfunction tests in the opendbc suite exercise the software reaction, not the relay</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
           </r>
         </is>
       </c>
       <c r="L15" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M15" s="37" t="inlineStr">
         <is>
@@ -4401,11 +4224,39 @@
             </rPr>
             <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
         </is>
       </c>
       <c r="O15" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P15" s="33" t="inlineStr"/>
@@ -4413,7 +4264,7 @@
       <c r="R15" s="39" t="inlineStr"/>
       <c r="S15" s="39" t="inlineStr"/>
     </row>
-    <row r="16" ht="87" customHeight="1">
+    <row r="16" ht="100.5" customHeight="1">
       <c r="A16" s="30" t="inlineStr">
         <is>
           <r>
@@ -4423,16 +4274,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-SE-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness, connectors, SBU orientation and ignition sense</t>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
           </r>
         </is>
       </c>
@@ -4445,16 +4296,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-FN-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
           </r>
         </is>
       </c>
@@ -4475,7 +4326,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss of lateral control while engaged</t>
+            <t>Erratic or excessive steering or braking</t>
           </r>
           <r>
             <rPr>
@@ -4493,6 +4344,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -4501,7 +4378,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Item disengages; relay releases if the coil loses drive</t>
+            <t>Conflicting steering and ACC commands</t>
           </r>
           <r>
             <rPr>
@@ -4527,13 +4404,14 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Panda loses CAN, power or relay drive</t>
+            <t>Stock camera LKA/ACC messages reach the car together with panda TX</t>
           </r>
         </is>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>HZ-004</t>
+          <t>HZ-002
+HZ-006</t>
         </is>
       </c>
       <c r="E16" s="32" t="n">
@@ -4548,17 +4426,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-012 · connection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness disconnected or intermittent while driving</t>
+            <t xml:space="preserve">DFM-011 · stuck
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch stays in pass-through when driven</t>
           </r>
         </is>
       </c>
@@ -4575,7 +4453,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Connector not fully latched at installation, or vibration loosens it</t>
+            <t>Analog switch U1 or U2 stuck in the pass-through (NC) position, or SBU1 drive lost or held low (driver open, R2/R3 short)</t>
           </r>
         </is>
       </c>
@@ -4587,7 +4465,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• Owner installation per comma instructions; no LionDriver installation check yet (WP-O-01)</t>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
           </r>
           <r>
             <rPr>
@@ -4596,12 +4474,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
         </is>
       </c>
       <c r="J16" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K16" s="34" t="inlineStr">
         <is>
@@ -4611,12 +4489,21 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+            <t>• Relay-malfunction tests in the opendbc suite exercise the software reaction, not the relay</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
           </r>
         </is>
       </c>
       <c r="L16" s="36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M16" s="37" t="inlineStr">
         <is>
@@ -4632,16 +4519,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-008 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+            <t xml:space="preserve">DFM-ACT-007 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
           </r>
         </is>
       </c>
@@ -4717,7 +4604,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock AEB unavailable</t>
+            <t>Loss of lateral control while engaged</t>
           </r>
           <r>
             <rPr>
@@ -4743,7 +4630,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>No stock PCS messages to the car</t>
+            <t>Item disengages; relay releases if the coil loses drive</t>
           </r>
           <r>
             <rPr>
@@ -4769,13 +4656,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Camera disconnected from the car</t>
+            <t>Panda loses CAN, power or relay drive</t>
           </r>
         </is>
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>HZ-011</t>
+          <t>HZ-004</t>
         </is>
       </c>
       <c r="E17" s="32" t="n">
@@ -4790,17 +4677,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-013 · open
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock camera path open inside the relay box</t>
+            <t xml:space="preserve">DFM-012 · connection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness disconnected or intermittent while driving</t>
           </r>
         </is>
       </c>
@@ -4817,7 +4704,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Open circuit in the relay box stock path (solder joint, contact)</t>
+            <t>Connector not fully latched at installation, or vibration loosens it</t>
           </r>
         </is>
       </c>
@@ -4829,7 +4716,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+            <t>• Owner installation per comma instructions; no LionDriver installation check yet (WP-O-01)</t>
           </r>
           <r>
             <rPr>
@@ -4838,12 +4725,12 @@
               <sz val="8"/>
             </rPr>
             <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
           </r>
         </is>
       </c>
       <c r="J17" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" s="34" t="inlineStr">
         <is>
@@ -4959,7 +4846,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Longer actuation window after SoC loss</t>
+            <t>Stock AEB unavailable</t>
           </r>
           <r>
             <rPr>
@@ -4985,7 +4872,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Slower withdrawal after SoC loss; device stays powered</t>
+            <t>No stock PCS messages to the car</t>
           </r>
           <r>
             <rPr>
@@ -5011,13 +4898,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Heartbeat timeout uses the 5 s ignition-on value</t>
+            <t>Camera disconnected from the car</t>
           </r>
         </is>
       </c>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>HZ-002</t>
+          <t>HZ-011</t>
         </is>
       </c>
       <c r="E18" s="32" t="n">
@@ -5032,17 +4919,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-014 · short
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Ignition sense reads on when the ignition is off</t>
+            <t xml:space="preserve">DFM-013 · open
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock camera path open inside the harness box</t>
           </r>
         </is>
       </c>
@@ -5059,7 +4946,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Ignition sense line shorted</t>
+            <t>Open in the harness box stock path (U1/U2 channel open, solder joint, connector contact)</t>
           </r>
         </is>
       </c>
@@ -5139,52 +5026,52 @@
       <c r="R18" s="39" t="inlineStr"/>
       <c r="S18" s="39" t="inlineStr"/>
     </row>
-    <row r="19" ht="154.5" customHeight="1">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
-          </r>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
-          </r>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
+    <row r="19" ht="87" customHeight="1">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness, connectors, SBU orientation and ignition sense</t>
+          </r>
+        </is>
+      </c>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
+          </r>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5201,7 +5088,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong in-envelope actuation, or a wrong configuration request</t>
+            <t>Longer actuation window after SoC loss</t>
           </r>
           <r>
             <rPr>
@@ -5227,7 +5114,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong command executed; a TX frame still passes the envelope checks</t>
+            <t>Slower withdrawal after SoC loss; device stays powered</t>
           </r>
           <r>
             <rPr>
@@ -5253,59 +5140,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A command or CAN frame is changed in transit and passes the 8-bit XOR</t>
-          </r>
-        </is>
-      </c>
-      <c r="D19" s="31" t="inlineStr">
+            <t>Heartbeat timeout uses the 5 s ignition-on value</t>
+          </r>
+        </is>
+      </c>
+      <c r="D19" s="41" t="inlineStr">
         <is>
           <t>HZ-002</t>
         </is>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="E19" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-015 · emc
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Corrupted SoC-to-MCU transfer accepted</t>
-          </r>
-        </is>
-      </c>
-      <c r="G19" s="33" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-014 · short
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition sense reads on when the ignition is off</t>
+          </r>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H19" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bit errors on the SPI link (EMC, signal integrity); 8-bit XOR only, no sequence counter</t>
-          </r>
-        </is>
-      </c>
-      <c r="I19" s="34" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition sense line shorted</t>
+          </r>
+        </is>
+      </c>
+      <c r="I19" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5324,38 +5211,12 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (reference build only)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   panda/board/drivers/spi.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="J19" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" s="34" t="inlineStr">
+        </is>
+      </c>
+      <c r="J19" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5367,225 +5228,56 @@
           </r>
         </is>
       </c>
-      <c r="L19" s="36" t="n">
+      <c r="L19" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M19" s="37" t="inlineStr">
+      <c r="M19" s="47" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N19" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-009 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Replace the 8-bit XOR with a CRC and add a sequence counter on the SoC-MCU link (GAP-10)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O19" s="38" t="inlineStr">
+      <c r="N19" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-008 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O19" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P19" s="33" t="inlineStr"/>
-      <c r="Q19" s="33" t="inlineStr"/>
-      <c r="R19" s="39" t="inlineStr"/>
-      <c r="S19" s="39" t="inlineStr"/>
+      <c r="P19" s="43" t="inlineStr"/>
+      <c r="Q19" s="43" t="inlineStr"/>
+      <c r="R19" s="49" t="inlineStr"/>
+      <c r="S19" s="49" t="inlineStr"/>
     </row>
-    <row r="20" ht="100.5" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
-          </r>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
-          </r>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Any actuation hazard (unverified image), or loss of function</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-005</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Without a safety model, or with an unsigned image</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The MCU runs no or unverified safety firmware</t>
-          </r>
-        </is>
-      </c>
-      <c r="D20" s="31" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-005</t>
-        </is>
-      </c>
-      <c r="E20" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-016 · connection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>MCU forced into the ROM bootloader or reflashed by the SoC</t>
-          </r>
-        </is>
-      </c>
+    <row r="20" ht="181.5" customHeight="1">
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
+      <c r="F20" s="50" t="n"/>
       <c r="G20" s="33" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H20" s="34" t="inlineStr">
@@ -5596,7 +5288,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>SoC drives STM_BOOT0/STM_RST_N (fault or compromise); no RDP/WRP; pandad recovery flashes a development bootstub</t>
+            <t>Ignition-sense transistor Q6 (DMN3200U, harness box) drain-source short, holding SBU2 low</t>
           </r>
         </is>
       </c>
@@ -5622,7 +5314,7 @@
         </is>
       </c>
       <c r="J20" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="34" t="inlineStr">
         <is>
@@ -5653,22 +5345,50 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-010 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement D-09/D-10: LionDriver signing key, no debug key in release builds, WRP + RDP1, remove the development-bootstub recovery (LD-DES-001 DR-10..DR-16)</t>
+            <t xml:space="preserve">DFM-ACT-008 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
           </r>
         </is>
       </c>
       <c r="O20" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P20" s="33" t="inlineStr"/>
@@ -5676,52 +5396,52 @@
       <c r="R20" s="39" t="inlineStr"/>
       <c r="S20" s="39" t="inlineStr"/>
     </row>
-    <row r="21" ht="87" customHeight="1">
-      <c r="A21" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-009
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-independent acoustic warning path (siren)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sound a warning when the SoC is lost while engaged, independently of the SoC audio</t>
-          </r>
-        </is>
-      </c>
-      <c r="C21" s="40" t="inlineStr">
+    <row r="21" ht="154.5" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
+          </r>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
+          </r>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5738,7 +5458,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss of control without timely warning</t>
+            <t>Wrong in-envelope actuation, or a wrong configuration request</t>
           </r>
           <r>
             <rPr>
@@ -5756,15 +5476,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-012</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong command executed; a TX frame still passes the envelope checks</t>
           </r>
           <r>
             <rPr>
@@ -5782,32 +5502,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver not warned when control is withdrawn after SoC loss</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -5816,60 +5510,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Siren silent</t>
-          </r>
-        </is>
-      </c>
-      <c r="D21" s="41" t="inlineStr">
-        <is>
-          <t>HZ-004
-HZ-012</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="n">
+            <t>A command or CAN frame is changed in transit and passes the 8-bit XOR</t>
+          </r>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-017 · loss
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No SoC-independent warning on SoC loss</t>
-          </r>
-        </is>
-      </c>
-      <c r="G21" s="43" t="inlineStr">
+      <c r="F21" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-015 · emc
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Corrupted SoC-to-MCU transfer accepted</t>
+          </r>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H21" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Siren shares the codec, amplifier or speaker with the SoC audio, which the faulty SoC powers down</t>
-          </r>
-        </is>
-      </c>
-      <c r="I21" s="44" t="inlineStr">
+      <c r="H21" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bit errors on the SPI link (EMC, signal integrity); 8-bit XOR only, no sequence counter</t>
+          </r>
+        </is>
+      </c>
+      <c r="I21" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5888,12 +5581,38 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
-        </is>
-      </c>
-      <c r="J21" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="44" t="inlineStr">
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (reference build only)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/board/drivers/spi.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J21" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5905,56 +5624,225 @@
           </r>
         </is>
       </c>
-      <c r="L21" s="46" t="n">
+      <c r="L21" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="47" t="inlineStr">
+      <c r="M21" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N21" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-011 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O21" s="48" t="inlineStr">
+      <c r="N21" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-009 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Replace the 8-bit XOR with a CRC and add a sequence counter on the SoC-MCU link (GAP-10)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O21" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P21" s="43" t="inlineStr"/>
-      <c r="Q21" s="43" t="inlineStr"/>
-      <c r="R21" s="49" t="inlineStr"/>
-      <c r="S21" s="49" t="inlineStr"/>
+      <c r="P21" s="33" t="inlineStr"/>
+      <c r="Q21" s="33" t="inlineStr"/>
+      <c r="R21" s="39" t="inlineStr"/>
+      <c r="S21" s="39" t="inlineStr"/>
     </row>
-    <row r="22" ht="87" customHeight="1">
-      <c r="A22" s="50" t="n"/>
-      <c r="B22" s="50" t="n"/>
-      <c r="C22" s="50" t="n"/>
-      <c r="D22" s="50" t="n"/>
-      <c r="E22" s="50" t="n"/>
-      <c r="F22" s="50" t="n"/>
+    <row r="22" ht="100.5" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
+          </r>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
+          </r>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Any actuation hazard (unverified image), or loss of function</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Without a safety model, or with an unsigned image</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The MCU runs no or unverified safety firmware</t>
+          </r>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-016 · connection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>MCU forced into the ROM bootloader or reflashed by the SoC</t>
+          </r>
+        </is>
+      </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H22" s="34" t="inlineStr">
@@ -5965,7 +5853,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Siren path fault stays latent (no self-test)</t>
+            <t>SoC drives STM_BOOT0/STM_RST_N (fault or compromise); no RDP/WRP; pandad recovery flashes a development bootstub</t>
           </r>
         </is>
       </c>
@@ -6022,16 +5910,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-011 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+            <t xml:space="preserve">DFM-ACT-010 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement D-09/D-10: LionDriver signing key, no debug key in release builds, WRP + RDP1, remove the development-bootstub recovery (LD-DES-001 DR-10..DR-16)</t>
           </r>
         </is>
       </c>
@@ -6045,8 +5933,377 @@
       <c r="R22" s="39" t="inlineStr"/>
       <c r="S22" s="39" t="inlineStr"/>
     </row>
-    <row r="23" ht="141" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+    <row r="23" ht="87" customHeight="1">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-009
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-independent acoustic warning path (siren)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sound a warning when the SoC is lost while engaged, independently of the SoC audio</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of control without timely warning</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-012</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not warned when control is withdrawn after SoC loss</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren silent</t>
+          </r>
+        </is>
+      </c>
+      <c r="D23" s="41" t="inlineStr">
+        <is>
+          <t>HZ-004
+HZ-012</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-017 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No SoC-independent warning on SoC loss</t>
+          </r>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H23" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren shares the codec, amplifier or speaker with the SoC audio, which the faulty SoC powers down</t>
+          </r>
+        </is>
+      </c>
+      <c r="I23" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J23" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L23" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N23" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-011 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O23" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P23" s="43" t="inlineStr"/>
+      <c r="Q23" s="43" t="inlineStr"/>
+      <c r="R23" s="49" t="inlineStr"/>
+      <c r="S23" s="49" t="inlineStr"/>
+    </row>
+    <row r="24" ht="87" customHeight="1">
+      <c r="A24" s="50" t="n"/>
+      <c r="B24" s="50" t="n"/>
+      <c r="C24" s="50" t="n"/>
+      <c r="D24" s="50" t="n"/>
+      <c r="E24" s="50" t="n"/>
+      <c r="F24" s="50" t="n"/>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H24" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren path fault stays latent (no self-test)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I24" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L24" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N24" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-011 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O24" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P24" s="33" t="inlineStr"/>
+      <c r="Q24" s="33" t="inlineStr"/>
+      <c r="R24" s="39" t="inlineStr"/>
+      <c r="S24" s="39" t="inlineStr"/>
+    </row>
+    <row r="25" ht="141" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6068,7 +6325,7 @@
           </r>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6090,7 +6347,7 @@
           </r>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6189,16 +6446,16 @@
           </r>
         </is>
       </c>
-      <c r="D23" s="31" t="inlineStr">
+      <c r="D25" s="31" t="inlineStr">
         <is>
           <t>HZ-002
 HZ-004</t>
         </is>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E25" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="30" t="inlineStr">
+      <c r="F25" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6221,12 +6478,12 @@
           </r>
         </is>
       </c>
-      <c r="G23" s="33" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H23" s="34" t="inlineStr">
+      <c r="H25" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6238,7 +6495,7 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="34" t="inlineStr">
+      <c r="I25" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6285,430 +6542,8 @@
           </r>
         </is>
       </c>
-      <c r="J23" s="35" t="n">
+      <c r="J25" s="35" t="n">
         <v>4</v>
-      </c>
-      <c r="K23" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L23" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="M23" s="37" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N23" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-012 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>React to MCU DTS out of range with the safe state (HWSR-509, DC-10); obtain the MCU temperature grade (UK-02)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O23" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P23" s="33" t="inlineStr"/>
-      <c r="Q23" s="33" t="inlineStr"/>
-      <c r="R23" s="39" t="inlineStr"/>
-      <c r="S23" s="39" t="inlineStr"/>
-    </row>
-    <row r="24" ht="127.5" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-002
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Safety MCU STM32H725: core, flash, SRAM</t>
-          </r>
-        </is>
-      </c>
-      <c r="B24" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-004
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Transmit and receive on buses 0, 1 and 2 without disturbing the vehicle bus</t>
-          </r>
-        </is>
-      </c>
-      <c r="C24" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Steering torque above the controllable bound</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-005 (acceleration above the bound)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006 (deceleration below the bound)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Out-of-envelope steering or acceleration frame reaches the vehicle with a valid CAN CRC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>A frame that passed safety_tx_hook changes in the FDCAN message RAM, the FDCAN core or the transceiver</t>
-          </r>
-        </is>
-      </c>
-      <c r="D24" s="41" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-005
-HZ-006</t>
-        </is>
-      </c>
-      <c r="E24" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F24" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-019 · intermittent
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Approved CAN frame altered between the TX check and the bus</t>
-          </r>
-        </is>
-      </c>
-      <c r="G24" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H24" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Soft error or permanent fault in the copy into FDCAN message RAM, the message RAM or the FDCAN core. The packet XOR is checked at the FDCAN load (fdcan.h:100) and covers only the software queue; the CAN CRC is computed after the fault</t>
-          </r>
-        </is>
-      </c>
-      <c r="I24" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Packet XOR checked before the FDCAN load (software queue only)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   panda/board/drivers/fdcan.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L24" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M24" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N24" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-013 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
-          </r>
-        </is>
-      </c>
-      <c r="O24" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P24" s="43" t="inlineStr"/>
-      <c r="Q24" s="43" t="inlineStr"/>
-      <c r="R24" s="49" t="inlineStr"/>
-      <c r="S24" s="49" t="inlineStr"/>
-    </row>
-    <row r="25" ht="87" customHeight="1">
-      <c r="A25" s="50" t="n"/>
-      <c r="B25" s="50" t="n"/>
-      <c r="C25" s="50" t="n"/>
-      <c r="D25" s="50" t="n"/>
-      <c r="E25" s="50" t="n"/>
-      <c r="F25" s="50" t="n"/>
-      <c r="G25" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H25" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Transceiver fault that changes bits on TX without a CAN error (not credible for a single bit, which the CAN CRC and the bit monitoring of the transmitting controller detect; kept until the transceiver part is known, WP-H-02 UK-01)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I25" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="J25" s="35" t="n">
-        <v>2</v>
       </c>
       <c r="K25" s="34" t="inlineStr">
         <is>
@@ -6739,16 +6574,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-013 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
+            <t xml:space="preserve">DFM-ACT-012 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>React to MCU DTS out of range with the safe state (HWSR-509, DC-10); obtain the MCU temperature grade (UK-02)</t>
           </r>
         </is>
       </c>
@@ -6762,40 +6597,1112 @@
       <c r="R25" s="39" t="inlineStr"/>
       <c r="S25" s="39" t="inlineStr"/>
     </row>
+    <row r="26" ht="127.5" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-002
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Safety MCU STM32H725: core, flash, SRAM</t>
+          </r>
+        </is>
+      </c>
+      <c r="B26" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-004
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Transmit and receive on buses 0, 1 and 2 without disturbing the vehicle bus</t>
+          </r>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Steering torque above the controllable bound</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005 (acceleration above the bound)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (deceleration below the bound)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Out-of-envelope steering or acceleration frame reaches the vehicle with a valid CAN CRC</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>A frame that passed safety_tx_hook changes in the FDCAN message RAM, the FDCAN core or the transceiver</t>
+          </r>
+        </is>
+      </c>
+      <c r="D26" s="41" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E26" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F26" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-019 · intermittent
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Approved CAN frame altered between the TX check and the bus</t>
+          </r>
+        </is>
+      </c>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H26" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Soft error or permanent fault in the copy into FDCAN message RAM, the message RAM or the FDCAN core. The packet XOR is checked at the FDCAN load (fdcan.h:100) and covers only the software queue; the CAN CRC is computed after the fault</t>
+          </r>
+        </is>
+      </c>
+      <c r="I26" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Packet XOR checked before the FDCAN load (software queue only)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/board/drivers/fdcan.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L26" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N26" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-013 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
+          </r>
+        </is>
+      </c>
+      <c r="O26" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P26" s="43" t="inlineStr"/>
+      <c r="Q26" s="43" t="inlineStr"/>
+      <c r="R26" s="49" t="inlineStr"/>
+      <c r="S26" s="49" t="inlineStr"/>
+    </row>
+    <row r="27" ht="87" customHeight="1">
+      <c r="A27" s="50" t="n"/>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+      <c r="E27" s="50" t="n"/>
+      <c r="F27" s="50" t="n"/>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H27" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Transceiver fault that changes bits on TX without a CAN error (not credible for a single bit, which the CAN CRC and the bit monitoring of the transmitting controller detect; kept until the transceiver part is known, WP-H-02 UK-01)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I27" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J27" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L27" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N27" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-013 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
+          </r>
+        </is>
+      </c>
+      <c r="O27" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P27" s="33" t="inlineStr"/>
+      <c r="Q27" s="33" t="inlineStr"/>
+      <c r="R27" s="39" t="inlineStr"/>
+      <c r="S27" s="39" t="inlineStr"/>
+    </row>
+    <row r="28" ht="127.5" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B28" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Lateral assist lost without a LionDriver warning</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock camera cut off from the car and the car-side ADAS CAN disturbed; the device is also unpowered</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>U1/U2 unpowered, so pass-through is not guaranteed; D2/D3 clamp CAN0 and CAN2 towards the dead VIN rail, which the device input loads (derived from the v3 drawing, to confirm on the bench)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D28" s="41" t="inlineStr">
+        <is>
+          <t>HZ-011
+HZ-004</t>
+        </is>
+      </c>
+      <c r="E28" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-020 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness box loses its supply while the car is on</t>
+          </r>
+        </is>
+      </c>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H28" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition branch to the box open (crimp, connector) or D1 open, without comma power installed</t>
+          </r>
+        </is>
+      </c>
+      <c r="I28" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L28" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N28" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O28" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P28" s="43" t="inlineStr"/>
+      <c r="Q28" s="43" t="inlineStr"/>
+      <c r="R28" s="49" t="inlineStr"/>
+      <c r="S28" s="49" t="inlineStr"/>
+    </row>
+    <row r="29" ht="127.5" customHeight="1">
+      <c r="A29" s="50" t="n"/>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+      <c r="E29" s="50" t="n"/>
+      <c r="F29" s="50" t="n"/>
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H29" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Box VIN shorted to ground (TVS D4 short, connector or wiring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I29" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L29" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N29" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O29" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P29" s="33" t="inlineStr"/>
+      <c r="Q29" s="33" t="inlineStr"/>
+      <c r="R29" s="39" t="inlineStr"/>
+      <c r="S29" s="39" t="inlineStr"/>
+    </row>
+    <row r="30" ht="127.5" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of lateral control with a late or no warning</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Car-side ADAS CAN or the camera bus cannot communicate; stock PCS messages lost</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>D2 (car side, CAN0) or D3 (camera side, CAN2) shorts a CAN line to GND or VIN in either switch state</t>
+          </r>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011
+HZ-004</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-021 · short
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Clamp diode short loads or grounds a vehicle bus in the harness box</t>
+          </r>
+        </is>
+      </c>
+      <c r="G30" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H30" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Schottky clamp D2 or D3 (BAS40SDW) short or leaky</t>
+          </r>
+        </is>
+      </c>
+      <c r="I30" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L30" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N30" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O30" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P30" s="33" t="inlineStr"/>
+      <c r="Q30" s="33" t="inlineStr"/>
+      <c r="R30" s="39" t="inlineStr"/>
+      <c r="S30" s="39" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S25"/>
-  <mergeCells count="28">
+  <autoFilter ref="A2:S30"/>
+  <mergeCells count="40">
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="E23:E24"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D28:D29"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A23:A24"/>
     <mergeCell ref="I1:M1"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="A19:A20"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E13:E15"/>
     <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="D26:D27"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B26:B27"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6803,7 +7710,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.4 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.5 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6818,7 +7725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6833,519 +7740,560 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="51" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E1" s="51" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="51" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>Causes</t>
         </is>
       </c>
-      <c r="G1" s="51" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>Revised S/O/D</t>
         </is>
       </c>
-      <c r="H1" s="51" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>Revised AP</t>
         </is>
       </c>
-      <c r="I1" s="51" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46.5" customHeight="1">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-001</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>prevention</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>Add a CPU self-test (vendor STL if available for STM32H7) at start-up and periodically, or argue the ASIL B target without CPU coverage (WP-H-03 finding 4)</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E2" s="52" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F2" s="52" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>DFM-001.C1</t>
         </is>
       </c>
-      <c r="G2" s="52" t="inlineStr"/>
-      <c r="H2" s="52" t="inlineStr"/>
-      <c r="I2" s="52" t="inlineStr"/>
+      <c r="G2" s="53" t="inlineStr"/>
+      <c r="H2" s="53" t="inlineStr"/>
+      <c r="I2" s="53" t="inlineStr"/>
     </row>
     <row r="3" ht="46.5" customHeight="1">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-002</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>Integrate the G1 layer 1 MCU measures (RAMECC handling, redundant storage, code CRC, start-up RAM test, fault escalation) from panda branch liondriver/g1-layer1 after review and HIL evidence</t>
         </is>
       </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F3" s="52" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
         <is>
           <t>DFM-002.C1
 DFM-003.C1
 DFM-003.C2</t>
         </is>
       </c>
-      <c r="G3" s="52" t="inlineStr"/>
-      <c r="H3" s="52" t="inlineStr"/>
-      <c r="I3" s="52" t="inlineStr"/>
+      <c r="G3" s="53" t="inlineStr"/>
+      <c r="H3" s="53" t="inlineStr"/>
+      <c r="I3" s="53" t="inlineStr"/>
     </row>
     <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-003</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C4" s="52" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04)</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F4" s="52" t="inlineStr">
+      <c r="F4" s="53" t="inlineStr">
         <is>
           <t>DFM-004.C1
 DFM-006.C1</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr"/>
-      <c r="H4" s="52" t="inlineStr"/>
-      <c r="I4" s="52" t="inlineStr"/>
+      <c r="G4" s="53" t="inlineStr"/>
+      <c r="H4" s="53" t="inlineStr"/>
+      <c r="I4" s="53" t="inlineStr"/>
     </row>
     <row r="5" ht="33" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-004</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Cross-check the HSE-derived time base against LSI or HSI and react on deviation (HWSR-504a)</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F5" s="52" t="inlineStr">
+      <c r="F5" s="53" t="inlineStr">
         <is>
           <t>DFM-005.C1</t>
         </is>
       </c>
-      <c r="G5" s="52" t="inlineStr"/>
-      <c r="H5" s="52" t="inlineStr"/>
-      <c r="I5" s="52" t="inlineStr"/>
+      <c r="G5" s="53" t="inlineStr"/>
+      <c r="H5" s="53" t="inlineStr"/>
+      <c r="I5" s="53" t="inlineStr"/>
     </row>
     <row r="6" ht="46.5" customHeight="1">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-005</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>Set the BOR level in the option bytes and enable PVD with a safe-state reaction (WP-H-02 DC-07); read the option bytes of a reference device (UK-04)</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F6" s="52" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>DFM-007.C1</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr"/>
-      <c r="H6" s="52" t="inlineStr"/>
-      <c r="I6" s="52" t="inlineStr"/>
+      <c r="G6" s="53" t="inlineStr"/>
+      <c r="H6" s="53" t="inlineStr"/>
+      <c r="I6" s="53" t="inlineStr"/>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-006</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C7" s="52" t="inlineStr">
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>Disable a transceiver and enter the safe state on persistent error or bus-off (HWSR-508, WP-H-02 DC-04)</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F7" s="52" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>DFM-008.C1
 DFM-009.C1</t>
         </is>
       </c>
-      <c r="G7" s="52" t="inlineStr"/>
-      <c r="H7" s="52" t="inlineStr"/>
-      <c r="I7" s="52" t="inlineStr"/>
+      <c r="G7" s="53" t="inlineStr"/>
+      <c r="H7" s="53" t="inlineStr"/>
+      <c r="I7" s="53" t="inlineStr"/>
     </row>
-    <row r="8" ht="46.5" customHeight="1">
-      <c r="A8" s="52" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-007</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F8" s="52" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>DFM-010.C1
 DFM-010.C2
+DFM-010.C3
 DFM-011.C1</t>
         </is>
       </c>
-      <c r="G8" s="52" t="inlineStr"/>
-      <c r="H8" s="52" t="inlineStr"/>
-      <c r="I8" s="52" t="inlineStr"/>
+      <c r="G8" s="53" t="inlineStr"/>
+      <c r="H8" s="53" t="inlineStr"/>
+      <c r="I8" s="53" t="inlineStr"/>
     </row>
-    <row r="9" ht="46.5" customHeight="1">
-      <c r="A9" s="52" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-008</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F9" s="52" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>DFM-012.C1
 DFM-013.C1
-DFM-014.C1</t>
-        </is>
-      </c>
-      <c r="G9" s="52" t="inlineStr"/>
-      <c r="H9" s="52" t="inlineStr"/>
-      <c r="I9" s="52" t="inlineStr"/>
+DFM-014.C1
+DFM-014.C2</t>
+        </is>
+      </c>
+      <c r="G9" s="53" t="inlineStr"/>
+      <c r="H9" s="53" t="inlineStr"/>
+      <c r="I9" s="53" t="inlineStr"/>
     </row>
     <row r="10" ht="33" customHeight="1">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-009</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C10" s="52" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>Replace the 8-bit XOR with a CRC and add a sequence counter on the SoC-MCU link (GAP-10)</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E10" s="52" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F10" s="52" t="inlineStr">
+      <c r="F10" s="53" t="inlineStr">
         <is>
           <t>DFM-015.C1</t>
         </is>
       </c>
-      <c r="G10" s="52" t="inlineStr"/>
-      <c r="H10" s="52" t="inlineStr"/>
-      <c r="I10" s="52" t="inlineStr"/>
+      <c r="G10" s="53" t="inlineStr"/>
+      <c r="H10" s="53" t="inlineStr"/>
+      <c r="I10" s="53" t="inlineStr"/>
     </row>
     <row r="11" ht="46.5" customHeight="1">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-010</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>Implement D-09/D-10: LionDriver signing key, no debug key in release builds, WRP + RDP1, remove the development-bootstub recovery (LD-DES-001 DR-10..DR-16)</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F11" s="52" t="inlineStr">
+      <c r="F11" s="53" t="inlineStr">
         <is>
           <t>DFM-016.C1</t>
         </is>
       </c>
-      <c r="G11" s="52" t="inlineStr"/>
-      <c r="H11" s="52" t="inlineStr"/>
-      <c r="I11" s="52" t="inlineStr"/>
+      <c r="G11" s="53" t="inlineStr"/>
+      <c r="H11" s="53" t="inlineStr"/>
+      <c r="I11" s="53" t="inlineStr"/>
     </row>
     <row r="12" ht="33" customHeight="1">
-      <c r="A12" s="52" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-011</t>
         </is>
       </c>
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="53" t="inlineStr">
         <is>
           <t>detection</t>
         </is>
       </c>
-      <c r="C12" s="52" t="inlineStr">
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
         </is>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E12" s="52" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F12" s="52" t="inlineStr">
+      <c r="F12" s="53" t="inlineStr">
         <is>
           <t>DFM-017.C1
 DFM-017.C2</t>
         </is>
       </c>
-      <c r="G12" s="52" t="inlineStr"/>
-      <c r="H12" s="52" t="inlineStr"/>
-      <c r="I12" s="52" t="inlineStr"/>
+      <c r="G12" s="53" t="inlineStr"/>
+      <c r="H12" s="53" t="inlineStr"/>
+      <c r="I12" s="53" t="inlineStr"/>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="52" t="inlineStr">
+      <c r="A13" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-012</t>
         </is>
       </c>
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C13" s="52" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>React to MCU DTS out of range with the safe state (HWSR-509, DC-10); obtain the MCU temperature grade (UK-02)</t>
         </is>
       </c>
-      <c r="D13" s="52" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E13" s="52" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F13" s="52" t="inlineStr">
+      <c r="F13" s="53" t="inlineStr">
         <is>
           <t>DFM-018.C1</t>
         </is>
       </c>
-      <c r="G13" s="52" t="inlineStr"/>
-      <c r="H13" s="52" t="inlineStr"/>
-      <c r="I13" s="52" t="inlineStr"/>
+      <c r="G13" s="53" t="inlineStr"/>
+      <c r="H13" s="53" t="inlineStr"/>
+      <c r="I13" s="53" t="inlineStr"/>
     </row>
     <row r="14" ht="46.5" customHeight="1">
-      <c r="A14" s="52" t="inlineStr">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-013</t>
         </is>
       </c>
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="53" t="inlineStr">
         <is>
           <t>design change</t>
         </is>
       </c>
-      <c r="C14" s="52" t="inlineStr">
+      <c r="C14" s="53" t="inlineStr">
         <is>
           <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
         </is>
       </c>
-      <c r="D14" s="52" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>Jherrod Thomas</t>
         </is>
       </c>
-      <c r="E14" s="52" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="F14" s="52" t="inlineStr">
+      <c r="F14" s="53" t="inlineStr">
         <is>
           <t>DFM-019.C1
 DFM-019.C2</t>
         </is>
       </c>
-      <c r="G14" s="52" t="inlineStr"/>
-      <c r="H14" s="52" t="inlineStr"/>
-      <c r="I14" s="52" t="inlineStr"/>
+      <c r="G14" s="53" t="inlineStr"/>
+      <c r="H14" s="53" t="inlineStr"/>
+      <c r="I14" s="53" t="inlineStr"/>
+    </row>
+    <row r="15" ht="73.5" customHeight="1">
+      <c r="A15" s="53" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="inlineStr">
+        <is>
+          <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+        </is>
+      </c>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr">
+        <is>
+          <t>DFM-010.C3
+DFM-014.C2
+DFM-020.C1
+DFM-020.C2
+DFM-021.C1</t>
+        </is>
+      </c>
+      <c r="G15" s="53" t="inlineStr"/>
+      <c r="H15" s="53" t="inlineStr"/>
+      <c r="I15" s="53" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7367,289 +8315,289 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>Element</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="51" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>Parent</t>
         </is>
       </c>
-      <c r="E1" s="51" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>Functions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="B2" s="52" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Item hardware: comma 3X with integrated panda, Toyota harness and relay box, installed in a Corolla E210 · ZRE212 · US (CFG-001)</t>
         </is>
       </c>
-      <c r="C2" s="52" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="D2" s="52" t="inlineStr"/>
-      <c r="E2" s="52" t="inlineStr"/>
+      <c r="D2" s="53" t="inlineStr"/>
+      <c r="E2" s="53" t="inlineStr"/>
     </row>
     <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-002</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    Safety MCU STM32H725: core, flash, SRAM</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>subsystem</t>
         </is>
       </c>
-      <c r="D3" s="52" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-001: Execute the safety model and hold its code, constants and state without corruption</t>
         </is>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-003</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">        MCU clock and independent watchdog (HSE, PLL, LSI, IWDG)</t>
         </is>
       </c>
-      <c r="C4" s="52" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-002</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-002: Provide an accurate time base for all timeouts, and reset the MCU (releasing the relay) within 0.1 s if execution stops</t>
         </is>
       </c>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-004</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    MCU power supply and supervision (board regulator, SMPS/LDO, BOR, PVD)</t>
         </is>
       </c>
-      <c r="C5" s="52" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D5" s="52" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E5" s="52" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-003: Supply the MCU within its operating range, or hold it in reset</t>
         </is>
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="52" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-005</t>
         </is>
       </c>
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    CAN transceivers XCVR1-4 and enables</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D6" s="52" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E6" s="52" t="inlineStr">
+      <c r="E6" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-004: Transmit and receive on buses 0, 1 and 2 without disturbing the vehicle bus</t>
         </is>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-006</t>
         </is>
       </c>
-      <c r="B7" s="52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Intercept relay and relay driver</t>
-        </is>
-      </c>
-      <c r="C7" s="52" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Intercept switch (harness box U1/U2) and its drive</t>
+        </is>
+      </c>
+      <c r="C7" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D7" s="52" t="inlineStr">
+      <c r="D7" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E7" s="52" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-005: Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
         </is>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1">
-      <c r="A8" s="52" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-007</t>
         </is>
       </c>
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    Harness, connectors, SBU orientation and ignition sense</t>
         </is>
       </c>
-      <c r="C8" s="52" t="inlineStr">
+      <c r="C8" s="53" t="inlineStr">
         <is>
           <t>interface</t>
         </is>
       </c>
-      <c r="D8" s="52" t="inlineStr">
+      <c r="D8" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E8" s="52" t="inlineStr">
+      <c r="E8" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-006: Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
         </is>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="52" t="inlineStr">
+      <c r="A9" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-008</t>
         </is>
       </c>
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr">
+      <c r="C9" s="53" t="inlineStr">
         <is>
           <t>interface</t>
         </is>
       </c>
-      <c r="D9" s="52" t="inlineStr">
+      <c r="D9" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E9" s="52" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-007: Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="52" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-009</t>
         </is>
       </c>
-      <c r="B10" s="52" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    SoC-independent acoustic warning path (siren)</t>
         </is>
       </c>
-      <c r="C10" s="52" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E10" s="52" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-008: Sound a warning when the SoC is lost while engaged, independently of the SoC audio</t>
         </is>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="52" t="inlineStr">
+      <c r="A11" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-010</t>
         </is>
       </c>
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">    Enclosure, windscreen mount and cooling (fan, DTS)</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>component</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>DFM-SE-001</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>DFM-FN-009: Keep the device mechanically secured and within its thermal operating range</t>
         </is>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -781,7 +781,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.5 · draft</t>
+          <t>0.6 · draft</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -910,7 +910,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>14 (14)</t>
+          <t>15 (15)</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4137,18 +4137,18 @@
       <c r="S14" s="49" t="inlineStr"/>
     </row>
     <row r="15" ht="181.5" customHeight="1">
-      <c r="A15" s="50" t="n"/>
-      <c r="B15" s="50" t="n"/>
-      <c r="C15" s="50" t="n"/>
-      <c r="D15" s="50" t="n"/>
-      <c r="E15" s="50" t="n"/>
-      <c r="F15" s="50" t="n"/>
-      <c r="G15" s="33" t="inlineStr">
+      <c r="A15" s="51" t="n"/>
+      <c r="B15" s="51" t="n"/>
+      <c r="C15" s="51" t="n"/>
+      <c r="D15" s="51" t="n"/>
+      <c r="E15" s="51" t="n"/>
+      <c r="F15" s="51" t="n"/>
+      <c r="G15" s="43" t="inlineStr">
         <is>
           <t>C3</t>
         </is>
       </c>
-      <c r="H15" s="34" t="inlineStr">
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4160,7 +4160,7 @@
           </r>
         </is>
       </c>
-      <c r="I15" s="34" t="inlineStr">
+      <c r="I15" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4181,10 +4181,10 @@
           </r>
         </is>
       </c>
-      <c r="J15" s="35" t="n">
+      <c r="J15" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="34" t="inlineStr">
+      <c r="K15" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4196,15 +4196,15 @@
           </r>
         </is>
       </c>
-      <c r="L15" s="36" t="n">
+      <c r="L15" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M15" s="37" t="inlineStr">
+      <c r="M15" s="47" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N15" s="34" t="inlineStr">
+      <c r="N15" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4253,196 +4253,27 @@
           </r>
         </is>
       </c>
-      <c r="O15" s="38" t="inlineStr">
+      <c r="O15" s="48" t="inlineStr">
         <is>
           <t>open
 open</t>
         </is>
       </c>
-      <c r="P15" s="33" t="inlineStr"/>
-      <c r="Q15" s="33" t="inlineStr"/>
-      <c r="R15" s="39" t="inlineStr"/>
-      <c r="S15" s="39" t="inlineStr"/>
+      <c r="P15" s="43" t="inlineStr"/>
+      <c r="Q15" s="43" t="inlineStr"/>
+      <c r="R15" s="49" t="inlineStr"/>
+      <c r="S15" s="49" t="inlineStr"/>
     </row>
-    <row r="16" ht="100.5" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Intercept switch (harness box U1/U2) and its drive</t>
-          </r>
-        </is>
-      </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
-          </r>
-        </is>
-      </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Erratic or excessive steering or braking</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Conflicting steering and ACC commands</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock camera LKA/ACC messages reach the car together with panda TX</t>
-          </r>
-        </is>
-      </c>
-      <c r="D16" s="31" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-006</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F16" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-011 · stuck
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Intercept switch stays in pass-through when driven</t>
-          </r>
-        </is>
-      </c>
+    <row r="16" ht="276" customHeight="1">
+      <c r="A16" s="50" t="n"/>
+      <c r="B16" s="50" t="n"/>
+      <c r="C16" s="50" t="n"/>
+      <c r="D16" s="50" t="n"/>
+      <c r="E16" s="50" t="n"/>
+      <c r="F16" s="50" t="n"/>
       <c r="G16" s="33" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="H16" s="34" t="inlineStr">
@@ -4453,7 +4284,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Analog switch U1 or U2 stuck in the pass-through (NC) position, or SBU1 drive lost or held low (driver open, R2/R3 short)</t>
+            <t>U1/U2 overstressed or latched up by box supply transients above the DG419LE absolute maximum (V+ = VL = VIN with no regulator; the SMF16A clamp D4 only starts to conduct above its 16 V stand-off). Damage can leave the switch in either position or open a channel (also DFM-011, DFM-013)</t>
           </r>
         </is>
       </c>
@@ -4476,10 +4307,36 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• D4 SMF16A TVS on VIN (harness box v3). Its clamp level against the DG419LE rating is not shown: datasheet limits not confirmed (RR-2026-010 F-05)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/reviews/RR-2026-010.md</t>
+          </r>
         </is>
       </c>
       <c r="J16" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" s="34" t="inlineStr">
         <is>
@@ -4489,21 +4346,12 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• Relay-malfunction tests in the opendbc suite exercise the software reaction, not the relay</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
           </r>
         </is>
       </c>
       <c r="L16" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="37" t="inlineStr">
         <is>
@@ -4519,22 +4367,50 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-007 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-015 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Read the Vishay DG417LE/DG418LE/DG419LE datasheet (document 76432) and record the absolute maximum V+ to V-, VL and IN ratings, the single-supply operating range and VINH/VINL at VL = V+ = 14 V; compare with VIN including the D4 clamp level. If a limit is exceeded, raise it with comma.ai and with DQ-209 (RR-2026-010 F-05; blocked at 2026-10-16: vendor and datasheet hosts unreachable from the analysis environment)</t>
           </r>
         </is>
       </c>
       <c r="O16" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P16" s="33" t="inlineStr"/>
@@ -4543,51 +4419,51 @@
       <c r="S16" s="39" t="inlineStr"/>
     </row>
     <row r="17" ht="87" customHeight="1">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness, connectors, SBU orientation and ignition sense</t>
-          </r>
-        </is>
-      </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
-          </r>
-        </is>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4604,7 +4480,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss of lateral control while engaged</t>
+            <t>Erratic or excessive steering or braking</t>
           </r>
           <r>
             <rPr>
@@ -4622,6 +4498,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -4630,7 +4532,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Item disengages; relay releases if the coil loses drive</t>
+            <t>Conflicting steering and ACC commands</t>
           </r>
           <r>
             <rPr>
@@ -4656,301 +4558,60 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Panda loses CAN, power or relay drive</t>
-          </r>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>HZ-004</t>
-        </is>
-      </c>
-      <c r="E17" s="32" t="n">
+            <t>Stock camera LKA/ACC messages reach the car together with panda TX</t>
+          </r>
+        </is>
+      </c>
+      <c r="D17" s="41" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-006</t>
+        </is>
+      </c>
+      <c r="E17" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="F17" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-012 · connection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness disconnected or intermittent while driving</t>
-          </r>
-        </is>
-      </c>
-      <c r="G17" s="33" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-011 · stuck
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch stays in pass-through when driven</t>
+          </r>
+        </is>
+      </c>
+      <c r="G17" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H17" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Connector not fully latched at installation, or vibration loosens it</t>
-          </r>
-        </is>
-      </c>
-      <c r="I17" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Owner installation per comma instructions; no LionDriver installation check yet (WP-O-01)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="J17" s="35" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="M17" s="37" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N17" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-008 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O17" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P17" s="33" t="inlineStr"/>
-      <c r="Q17" s="33" t="inlineStr"/>
-      <c r="R17" s="39" t="inlineStr"/>
-      <c r="S17" s="39" t="inlineStr"/>
-    </row>
-    <row r="18" ht="87" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness, connectors, SBU orientation and ignition sense</t>
-          </r>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
-          </r>
-        </is>
-      </c>
-      <c r="C18" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock AEB unavailable</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No stock PCS messages to the car</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Camera disconnected from the car</t>
-          </r>
-        </is>
-      </c>
-      <c r="D18" s="31" t="inlineStr">
-        <is>
-          <t>HZ-011</t>
-        </is>
-      </c>
-      <c r="E18" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-013 · open
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Stock camera path open inside the harness box</t>
-          </r>
-        </is>
-      </c>
-      <c r="G18" s="33" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H18" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Open in the harness box stock path (U1/U2 channel open, solder joint, connector contact)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I18" s="34" t="inlineStr">
+      <c r="H17" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Analog switch U1 or U2 stuck in the pass-through (NC) position, or SBU1 drive lost or held low (driver open, R2/R3 short)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I17" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4971,8 +4632,143 @@
           </r>
         </is>
       </c>
+      <c r="J17" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Relay-malfunction tests in the opendbc suite exercise the software reaction, not the relay</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
+          </r>
+        </is>
+      </c>
+      <c r="L17" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="M17" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N17" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-007 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O17" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P17" s="43" t="inlineStr"/>
+      <c r="Q17" s="43" t="inlineStr"/>
+      <c r="R17" s="49" t="inlineStr"/>
+      <c r="S17" s="49" t="inlineStr"/>
+    </row>
+    <row r="18" ht="276" customHeight="1">
+      <c r="A18" s="50" t="n"/>
+      <c r="B18" s="50" t="n"/>
+      <c r="C18" s="50" t="n"/>
+      <c r="D18" s="50" t="n"/>
+      <c r="E18" s="50" t="n"/>
+      <c r="F18" s="50" t="n"/>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H18" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The 5 V SBU1 drive does not reach the DG419LE logic-high threshold with VL tied to VIN (about 14 V), so the switch does not change over or changes over only at some temperatures (RR-2026-010 F-05; thresholds at VL = VIN not confirmed)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I18" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Field use: openpilot on TSS2 Toyotas with this box would raise relayMalfunction on every drive if the switch never changed over, which suggests it switches at nominal conditions. Margin over temperature and supply is not shown</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/reviews/RR-2026-010.md</t>
+          </r>
+        </is>
+      </c>
       <c r="J18" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="34" t="inlineStr">
         <is>
@@ -4982,12 +4778,21 @@
               <color rgb="008A5A00"/>
               <sz val="10"/>
             </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+            <t>• Relay-malfunction tests in the opendbc suite exercise the software reaction, not the switch threshold</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   opendbc_repo/opendbc/safety/tests/test_toyota.py</t>
           </r>
         </is>
       </c>
       <c r="L18" s="36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M18" s="37" t="inlineStr">
         <is>
@@ -5003,22 +4808,50 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-008 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-015 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Read the Vishay DG417LE/DG418LE/DG419LE datasheet (document 76432) and record the absolute maximum V+ to V-, VL and IN ratings, the single-supply operating range and VINH/VINL at VL = V+ = 14 V; compare with VIN including the D4 clamp level. If a limit is exceeded, raise it with comma.ai and with DQ-209 (RR-2026-010 F-05; blocked at 2026-10-16: vendor and datasheet hosts unreachable from the analysis environment)</t>
           </r>
         </is>
       </c>
       <c r="O18" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P18" s="33" t="inlineStr"/>
@@ -5027,7 +4860,7 @@
       <c r="S18" s="39" t="inlineStr"/>
     </row>
     <row r="19" ht="87" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5049,7 +4882,7 @@
           </r>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5071,7 +4904,7 @@
           </r>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5088,7 +4921,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Longer actuation window after SoC loss</t>
+            <t>Loss of lateral control while engaged</t>
           </r>
           <r>
             <rPr>
@@ -5114,7 +4947,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Slower withdrawal after SoC loss; device stays powered</t>
+            <t>Item disengages; relay releases if the coil loses drive</t>
           </r>
           <r>
             <rPr>
@@ -5140,59 +4973,301 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Heartbeat timeout uses the 5 s ignition-on value</t>
-          </r>
-        </is>
-      </c>
-      <c r="D19" s="41" t="inlineStr">
-        <is>
-          <t>HZ-002</t>
-        </is>
-      </c>
-      <c r="E19" s="42" t="n">
+            <t>Panda loses CAN, power or relay drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>HZ-004</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-014 · short
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Ignition sense reads on when the ignition is off</t>
-          </r>
-        </is>
-      </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-012 · connection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness disconnected or intermittent while driving</t>
+          </r>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H19" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Ignition sense line shorted</t>
-          </r>
-        </is>
-      </c>
-      <c r="I19" s="44" t="inlineStr">
+      <c r="H19" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Connector not fully latched at installation, or vibration loosens it</t>
+          </r>
+        </is>
+      </c>
+      <c r="I19" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Owner installation per comma instructions; no LionDriver installation check yet (WP-O-01)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/09-production-operation/WP-O-01-installation-and-provisioning-control.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N19" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-008 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O19" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P19" s="33" t="inlineStr"/>
+      <c r="Q19" s="33" t="inlineStr"/>
+      <c r="R19" s="39" t="inlineStr"/>
+      <c r="S19" s="39" t="inlineStr"/>
+    </row>
+    <row r="20" ht="87" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness, connectors, SBU orientation and ignition sense</t>
+          </r>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
+          </r>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No stock PCS messages to the car</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera disconnected from the car</t>
+          </r>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-013 · open
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock camera path open inside the harness box</t>
+          </r>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H20" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Open in the harness box stock path (U1/U2 channel open, solder joint, connector contact)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I20" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5213,106 +5288,6 @@
           </r>
         </is>
       </c>
-      <c r="J19" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L19" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M19" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N19" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-008 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O19" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P19" s="43" t="inlineStr"/>
-      <c r="Q19" s="43" t="inlineStr"/>
-      <c r="R19" s="49" t="inlineStr"/>
-      <c r="S19" s="49" t="inlineStr"/>
-    </row>
-    <row r="20" ht="181.5" customHeight="1">
-      <c r="A20" s="50" t="n"/>
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="50" t="n"/>
-      <c r="D20" s="50" t="n"/>
-      <c r="E20" s="50" t="n"/>
-      <c r="F20" s="50" t="n"/>
-      <c r="G20" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H20" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Ignition-sense transistor Q6 (DMN3200U, harness box) drain-source short, holding SBU2 low</t>
-          </r>
-        </is>
-      </c>
-      <c r="I20" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
-          </r>
-        </is>
-      </c>
       <c r="J20" s="35" t="n">
         <v>3</v>
       </c>
@@ -5356,39 +5331,11 @@
             </rPr>
             <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-014 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
-          </r>
         </is>
       </c>
       <c r="O20" s="38" t="inlineStr">
         <is>
-          <t>open
-open</t>
+          <t>open</t>
         </is>
       </c>
       <c r="P20" s="33" t="inlineStr"/>
@@ -5396,52 +5343,52 @@
       <c r="R20" s="39" t="inlineStr"/>
       <c r="S20" s="39" t="inlineStr"/>
     </row>
-    <row r="21" ht="154.5" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
-          </r>
-        </is>
-      </c>
-      <c r="B21" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
-          </r>
-        </is>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
+    <row r="21" ht="87" customHeight="1">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness, connectors, SBU orientation and ignition sense</t>
+          </r>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Connect the device to the vehicle buses, power and ignition, and report harness orientation correctly</t>
+          </r>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5458,7 +5405,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong in-envelope actuation, or a wrong configuration request</t>
+            <t>Longer actuation window after SoC loss</t>
           </r>
           <r>
             <rPr>
@@ -5484,7 +5431,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Wrong command executed; a TX frame still passes the envelope checks</t>
+            <t>Slower withdrawal after SoC loss; device stays powered</t>
           </r>
           <r>
             <rPr>
@@ -5510,59 +5457,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>A command or CAN frame is changed in transit and passes the 8-bit XOR</t>
-          </r>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
+            <t>Heartbeat timeout uses the 5 s ignition-on value</t>
+          </r>
+        </is>
+      </c>
+      <c r="D21" s="41" t="inlineStr">
         <is>
           <t>HZ-002</t>
         </is>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="E21" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-015 · emc
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Corrupted SoC-to-MCU transfer accepted</t>
-          </r>
-        </is>
-      </c>
-      <c r="G21" s="33" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-014 · short
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition sense reads on when the ignition is off</t>
+          </r>
+        </is>
+      </c>
+      <c r="G21" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H21" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bit errors on the SPI link (EMC, signal integrity); 8-bit XOR only, no sequence counter</t>
-          </r>
-        </is>
-      </c>
-      <c r="I21" s="34" t="inlineStr">
+      <c r="H21" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition sense line shorted</t>
+          </r>
+        </is>
+      </c>
+      <c r="I21" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5581,38 +5528,12 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (reference build only)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   panda/board/drivers/spi.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="J21" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="K21" s="34" t="inlineStr">
+        </is>
+      </c>
+      <c r="J21" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5624,225 +5545,56 @@
           </r>
         </is>
       </c>
-      <c r="L21" s="36" t="n">
+      <c r="L21" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="M21" s="37" t="inlineStr">
+      <c r="M21" s="47" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N21" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-009 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Replace the 8-bit XOR with a CRC and add a sequence counter on the SoC-MCU link (GAP-10)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O21" s="38" t="inlineStr">
+      <c r="N21" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-008 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O21" s="48" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P21" s="33" t="inlineStr"/>
-      <c r="Q21" s="33" t="inlineStr"/>
-      <c r="R21" s="39" t="inlineStr"/>
-      <c r="S21" s="39" t="inlineStr"/>
+      <c r="P21" s="43" t="inlineStr"/>
+      <c r="Q21" s="43" t="inlineStr"/>
+      <c r="R21" s="49" t="inlineStr"/>
+      <c r="S21" s="49" t="inlineStr"/>
     </row>
-    <row r="22" ht="100.5" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
-          </r>
-        </is>
-      </c>
-      <c r="B22" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-007
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
-          </r>
-        </is>
-      </c>
-      <c r="C22" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Any actuation hazard (unverified image), or loss of function</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-005</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Without a safety model, or with an unsigned image</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>The MCU runs no or unverified safety firmware</t>
-          </r>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-005</t>
-        </is>
-      </c>
-      <c r="E22" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="F22" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-016 · connection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>MCU forced into the ROM bootloader or reflashed by the SoC</t>
-          </r>
-        </is>
-      </c>
+    <row r="22" ht="181.5" customHeight="1">
+      <c r="A22" s="50" t="n"/>
+      <c r="B22" s="50" t="n"/>
+      <c r="C22" s="50" t="n"/>
+      <c r="D22" s="50" t="n"/>
+      <c r="E22" s="50" t="n"/>
+      <c r="F22" s="50" t="n"/>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="H22" s="34" t="inlineStr">
@@ -5853,7 +5605,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>SoC drives STM_BOOT0/STM_RST_N (fault or compromise); no RDP/WRP; pandad recovery flashes a development bootstub</t>
+            <t>Ignition-sense transistor Q6 (DMN3200U, harness box) drain-source short, holding SBU2 low</t>
           </r>
         </is>
       </c>
@@ -5879,7 +5631,7 @@
         </is>
       </c>
       <c r="J22" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" s="34" t="inlineStr">
         <is>
@@ -5910,22 +5662,50 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-010 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement D-09/D-10: LionDriver signing key, no debug key in release builds, WRP + RDP1, remove the development-bootstub recovery (LD-DES-001 DR-10..DR-16)</t>
+            <t xml:space="preserve">DFM-ACT-008 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Define the installation check, including a stock PCS/AEB function check and a harness latch check (WP-O-01, TSR-805)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
           </r>
         </is>
       </c>
       <c r="O22" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P22" s="33" t="inlineStr"/>
@@ -5933,52 +5713,52 @@
       <c r="R22" s="39" t="inlineStr"/>
       <c r="S22" s="39" t="inlineStr"/>
     </row>
-    <row r="23" ht="87" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-009
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>SoC-independent acoustic warning path (siren)</t>
-          </r>
-        </is>
-      </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-008
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Sound a warning when the SoC is lost while engaged, independently of the SoC audio</t>
-          </r>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
+    <row r="23" ht="154.5" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
+          </r>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
+          </r>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5995,7 +5775,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss of control without timely warning</t>
+            <t>Wrong in-envelope actuation, or a wrong configuration request</t>
           </r>
           <r>
             <rPr>
@@ -6013,15 +5793,15 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-012</t>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Wrong command executed; a TX frame still passes the envelope checks</t>
           </r>
           <r>
             <rPr>
@@ -6039,32 +5819,6 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Driver not warned when control is withdrawn after SoC loss</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
             <t xml:space="preserve">Local  </t>
           </r>
           <r>
@@ -6073,60 +5827,59 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Siren silent</t>
-          </r>
-        </is>
-      </c>
-      <c r="D23" s="41" t="inlineStr">
-        <is>
-          <t>HZ-004
-HZ-012</t>
-        </is>
-      </c>
-      <c r="E23" s="42" t="n">
+            <t>A command or CAN frame is changed in transit and passes the 8-bit XOR</t>
+          </r>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-017 · loss
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>No SoC-independent warning on SoC loss</t>
-          </r>
-        </is>
-      </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="F23" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-015 · emc
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Corrupted SoC-to-MCU transfer accepted</t>
+          </r>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H23" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Siren shares the codec, amplifier or speaker with the SoC audio, which the faulty SoC powers down</t>
-          </r>
-        </is>
-      </c>
-      <c r="I23" s="44" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bit errors on the SPI link (EMC, signal integrity); 8-bit XOR only, no sequence counter</t>
+          </r>
+        </is>
+      </c>
+      <c r="I23" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6145,12 +5898,38 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
-        </is>
-      </c>
-      <c r="J23" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="K23" s="44" t="inlineStr">
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (reference build only)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/board/drivers/spi.h</t>
+          </r>
+        </is>
+      </c>
+      <c r="J23" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6162,56 +5941,225 @@
           </r>
         </is>
       </c>
-      <c r="L23" s="46" t="n">
+      <c r="L23" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M23" s="47" t="inlineStr">
+      <c r="M23" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N23" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-011 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O23" s="48" t="inlineStr">
+      <c r="N23" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-009 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Replace the 8-bit XOR with a CRC and add a sequence counter on the SoC-MCU link (GAP-10)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O23" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P23" s="43" t="inlineStr"/>
-      <c r="Q23" s="43" t="inlineStr"/>
-      <c r="R23" s="49" t="inlineStr"/>
-      <c r="S23" s="49" t="inlineStr"/>
+      <c r="P23" s="33" t="inlineStr"/>
+      <c r="Q23" s="33" t="inlineStr"/>
+      <c r="R23" s="39" t="inlineStr"/>
+      <c r="S23" s="39" t="inlineStr"/>
     </row>
-    <row r="24" ht="87" customHeight="1">
-      <c r="A24" s="50" t="n"/>
-      <c r="B24" s="50" t="n"/>
-      <c r="C24" s="50" t="n"/>
-      <c r="D24" s="50" t="n"/>
-      <c r="E24" s="50" t="n"/>
-      <c r="F24" s="50" t="n"/>
+    <row r="24" ht="100.5" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-MCU interface: SPI link, STM_RST_N, STM_BOOT0</t>
+          </r>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-007
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Carry commands, CAN frames and heartbeat between SoC and MCU intact; keep the MCU running the signed application</t>
+          </r>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Any actuation hazard (unverified image), or loss of function</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-005</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Without a safety model, or with an unsigned image</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>The MCU runs no or unverified safety firmware</t>
+          </r>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>HZ-002
+HZ-005</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-016 · connection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>MCU forced into the ROM bootloader or reflashed by the SoC</t>
+          </r>
+        </is>
+      </c>
       <c r="G24" s="33" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="H24" s="34" t="inlineStr">
@@ -6222,7 +6170,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Siren path fault stays latent (no self-test)</t>
+            <t>SoC drives STM_BOOT0/STM_RST_N (fault or compromise); no RDP/WRP; pandad recovery flashes a development bootstub</t>
           </r>
         </is>
       </c>
@@ -6279,16 +6227,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-011 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+            <t xml:space="preserve">DFM-ACT-010 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement D-09/D-10: LionDriver signing key, no debug key in release builds, WRP + RDP1, remove the development-bootstub recovery (LD-DES-001 DR-10..DR-16)</t>
           </r>
         </is>
       </c>
@@ -6302,8 +6250,377 @@
       <c r="R24" s="39" t="inlineStr"/>
       <c r="S24" s="39" t="inlineStr"/>
     </row>
-    <row r="25" ht="141" customHeight="1">
-      <c r="A25" s="30" t="inlineStr">
+    <row r="25" ht="87" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-009
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>SoC-independent acoustic warning path (siren)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-008
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Sound a warning when the SoC is lost while engaged, independently of the SoC audio</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of control without timely warning</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-012</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Driver not warned when control is withdrawn after SoC loss</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren silent</t>
+          </r>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>HZ-004
+HZ-012</t>
+        </is>
+      </c>
+      <c r="E25" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-017 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No SoC-independent warning on SoC loss</t>
+          </r>
+        </is>
+      </c>
+      <c r="G25" s="43" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H25" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren shares the codec, amplifier or speaker with the SoC audio, which the faulty SoC powers down</t>
+          </r>
+        </is>
+      </c>
+      <c r="I25" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J25" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L25" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M25" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N25" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-011 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O25" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P25" s="43" t="inlineStr"/>
+      <c r="Q25" s="43" t="inlineStr"/>
+      <c r="R25" s="49" t="inlineStr"/>
+      <c r="S25" s="49" t="inlineStr"/>
+    </row>
+    <row r="26" ht="87" customHeight="1">
+      <c r="A26" s="50" t="n"/>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+      <c r="E26" s="50" t="n"/>
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H26" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Siren path fault stays latent (no self-test)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I26" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L26" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M26" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N26" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-011 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O26" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P26" s="33" t="inlineStr"/>
+      <c r="Q26" s="33" t="inlineStr"/>
+      <c r="R26" s="39" t="inlineStr"/>
+      <c r="S26" s="39" t="inlineStr"/>
+    </row>
+    <row r="27" ht="141" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6325,7 +6642,7 @@
           </r>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6347,7 +6664,7 @@
           </r>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6446,16 +6763,16 @@
           </r>
         </is>
       </c>
-      <c r="D25" s="31" t="inlineStr">
+      <c r="D27" s="31" t="inlineStr">
         <is>
           <t>HZ-002
 HZ-004</t>
         </is>
       </c>
-      <c r="E25" s="32" t="n">
+      <c r="E27" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="F25" s="30" t="inlineStr">
+      <c r="F27" s="30" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6478,12 +6795,12 @@
           </r>
         </is>
       </c>
-      <c r="G25" s="33" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H25" s="34" t="inlineStr">
+      <c r="H27" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6495,7 +6812,7 @@
           </r>
         </is>
       </c>
-      <c r="I25" s="34" t="inlineStr">
+      <c r="I27" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6542,430 +6859,8 @@
           </r>
         </is>
       </c>
-      <c r="J25" s="35" t="n">
+      <c r="J27" s="35" t="n">
         <v>4</v>
-      </c>
-      <c r="K25" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L25" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="37" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N25" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-012 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>React to MCU DTS out of range with the safe state (HWSR-509, DC-10); obtain the MCU temperature grade (UK-02)</t>
-          </r>
-        </is>
-      </c>
-      <c r="O25" s="38" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P25" s="33" t="inlineStr"/>
-      <c r="Q25" s="33" t="inlineStr"/>
-      <c r="R25" s="39" t="inlineStr"/>
-      <c r="S25" s="39" t="inlineStr"/>
-    </row>
-    <row r="26" ht="127.5" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-SE-002
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Safety MCU STM32H725: core, flash, SRAM</t>
-          </r>
-        </is>
-      </c>
-      <c r="B26" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-FN-004
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Transmit and receive on buses 0, 1 and 2 without disturbing the vehicle bus</t>
-          </r>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Steering torque above the controllable bound</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-005 (acceleration above the bound)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">End  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Contributes to HZ-006 (deceleration below the bound)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Next higher  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Out-of-envelope steering or acceleration frame reaches the vehicle with a valid CAN CRC</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="005B6676"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">Local  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>A frame that passed safety_tx_hook changes in the FDCAN message RAM, the FDCAN core or the transceiver</t>
-          </r>
-        </is>
-      </c>
-      <c r="D26" s="41" t="inlineStr">
-        <is>
-          <t>HZ-002
-HZ-005
-HZ-006</t>
-        </is>
-      </c>
-      <c r="E26" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="40" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-019 · intermittent
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Approved CAN frame altered between the TX check and the bus</t>
-          </r>
-        </is>
-      </c>
-      <c r="G26" s="43" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="H26" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Soft error or permanent fault in the copy into FDCAN message RAM, the message RAM or the FDCAN core. The packet XOR is checked at the FDCAN load (fdcan.h:100) and covers only the software queue; the CAN CRC is computed after the fault</t>
-          </r>
-        </is>
-      </c>
-      <c r="I26" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• Packet XOR checked before the FDCAN load (software queue only)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   panda/board/drivers/fdcan.h</t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="008A5A00"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
-          </r>
-        </is>
-      </c>
-      <c r="L26" s="46" t="n">
-        <v>10</v>
-      </c>
-      <c r="M26" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="N26" s="44" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-ACT-013 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
-          </r>
-        </is>
-      </c>
-      <c r="O26" s="48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="P26" s="43" t="inlineStr"/>
-      <c r="Q26" s="43" t="inlineStr"/>
-      <c r="R26" s="49" t="inlineStr"/>
-      <c r="S26" s="49" t="inlineStr"/>
-    </row>
-    <row r="27" ht="87" customHeight="1">
-      <c r="A27" s="50" t="n"/>
-      <c r="B27" s="50" t="n"/>
-      <c r="C27" s="50" t="n"/>
-      <c r="D27" s="50" t="n"/>
-      <c r="E27" s="50" t="n"/>
-      <c r="F27" s="50" t="n"/>
-      <c r="G27" s="33" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="H27" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Transceiver fault that changes bits on TX without a CAN error (not credible for a single bit, which the CAN CRC and the bit monitoring of the transmitting controller detect; kept until the transceiver part is known, WP-H-02 UK-01)</t>
-          </r>
-        </is>
-      </c>
-      <c r="I27" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="005B6676"/>
-              <sz val="8"/>
-            </rPr>
-            <t xml:space="preserve">
-   assurance/04-hardware/WP-H-02-hardware-design.md</t>
-          </r>
-        </is>
-      </c>
-      <c r="J27" s="35" t="n">
-        <v>2</v>
       </c>
       <c r="K27" s="34" t="inlineStr">
         <is>
@@ -6996,16 +6891,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-013 · design change
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
+            <t xml:space="preserve">DFM-ACT-012 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>React to MCU DTS out of range with the safe state (HWSR-509, DC-10); obtain the MCU temperature grade (UK-02)</t>
           </r>
         </is>
       </c>
@@ -7029,16 +6924,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-SE-006
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Intercept switch (harness box U1/U2) and its drive</t>
+            <t xml:space="preserve">DFM-SE-002
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Safety MCU STM32H725: core, flash, SRAM</t>
           </r>
         </is>
       </c>
@@ -7051,16 +6946,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-FN-005
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+            <t xml:space="preserve">DFM-FN-004
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Transmit and receive on buses 0, 1 and 2 without disturbing the vehicle bus</t>
           </r>
         </is>
       </c>
@@ -7081,7 +6976,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock AEB unavailable</t>
+            <t>Steering torque above the controllable bound</t>
           </r>
           <r>
             <rPr>
@@ -7107,7 +7002,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Lateral assist lost without a LionDriver warning</t>
+            <t>Contributes to HZ-005 (acceleration above the bound)</t>
           </r>
           <r>
             <rPr>
@@ -7125,6 +7020,32 @@
               <color rgb="005B6676"/>
               <sz val="9"/>
             </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Contributes to HZ-006 (deceleration below the bound)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
             <t xml:space="preserve">Next higher  </t>
           </r>
           <r>
@@ -7133,7 +7054,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Stock camera cut off from the car and the car-side ADAS CAN disturbed; the device is also unpowered</t>
+            <t>Out-of-envelope steering or acceleration frame reaches the vehicle with a valid CAN CRC</t>
           </r>
           <r>
             <rPr>
@@ -7159,14 +7080,15 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>U1/U2 unpowered, so pass-through is not guaranteed; D2/D3 clamp CAN0 and CAN2 towards the dead VIN rail, which the device input loads (derived from the v3 drawing, to confirm on the bench)</t>
+            <t>A frame that passed safety_tx_hook changes in the FDCAN message RAM, the FDCAN core or the transceiver</t>
           </r>
         </is>
       </c>
       <c r="D28" s="41" t="inlineStr">
         <is>
-          <t>HZ-011
-HZ-004</t>
+          <t>HZ-002
+HZ-005
+HZ-006</t>
         </is>
       </c>
       <c r="E28" s="42" t="n">
@@ -7181,17 +7103,17 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-020 · loss
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Harness box loses its supply while the car is on</t>
+            <t xml:space="preserve">DFM-019 · intermittent
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Approved CAN frame altered between the TX check and the bus</t>
           </r>
         </is>
       </c>
@@ -7208,7 +7130,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Ignition branch to the box open (crimp, connector) or D1 open, without comma power installed</t>
+            <t>Soft error or permanent fault in the copy into FDCAN message RAM, the message RAM or the FDCAN core. The packet XOR is checked at the FDCAN load (fdcan.h:100) and covers only the software queue; the CAN CRC is computed after the fault</t>
           </r>
         </is>
       </c>
@@ -7231,10 +7153,36 @@
             <t xml:space="preserve">
    assurance/04-hardware/WP-H-02-hardware-design.md</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• Packet XOR checked before the FDCAN load (software queue only)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   panda/board/drivers/fdcan.h</t>
+          </r>
         </is>
       </c>
       <c r="J28" s="45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K28" s="44" t="inlineStr">
         <is>
@@ -7265,16 +7213,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-014 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t xml:space="preserve">DFM-ACT-013 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
           </r>
         </is>
       </c>
@@ -7288,7 +7236,7 @@
       <c r="R28" s="49" t="inlineStr"/>
       <c r="S28" s="49" t="inlineStr"/>
     </row>
-    <row r="29" ht="127.5" customHeight="1">
+    <row r="29" ht="87" customHeight="1">
       <c r="A29" s="50" t="n"/>
       <c r="B29" s="50" t="n"/>
       <c r="C29" s="50" t="n"/>
@@ -7308,7 +7256,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Box VIN shorted to ground (TVS D4 short, connector or wiring)</t>
+            <t>Transceiver fault that changes bits on TX without a CAN error (not credible for a single bit, which the CAN CRC and the bit monitoring of the transmitting controller detect; kept until the transceiver part is known, WP-H-02 UK-01)</t>
           </r>
         </is>
       </c>
@@ -7334,7 +7282,7 @@
         </is>
       </c>
       <c r="J29" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K29" s="34" t="inlineStr">
         <is>
@@ -7365,16 +7313,16 @@
               <color rgb="001F4E8C"/>
               <sz val="9"/>
             </rPr>
-            <t xml:space="preserve">DFM-ACT-014 · detection
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t xml:space="preserve">DFM-ACT-013 · design change
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Implement TSR-517: read back the item's own TX frames from the bus and compare with the approved frame, revoking on a mismatch; enable RAMECC handling for the FDCAN message RAM if the H725 provides it</t>
           </r>
         </is>
       </c>
@@ -7389,7 +7337,7 @@
       <c r="S29" s="39" t="inlineStr"/>
     </row>
     <row r="30" ht="127.5" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7411,7 +7359,7 @@
           </r>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7433,7 +7381,7 @@
           </r>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="40" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7476,7 +7424,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Loss of lateral control with a late or no warning</t>
+            <t>Lateral assist lost without a LionDriver warning</t>
           </r>
           <r>
             <rPr>
@@ -7502,7 +7450,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Car-side ADAS CAN or the camera bus cannot communicate; stock PCS messages lost</t>
+            <t>Stock camera cut off from the car and the car-side ADAS CAN disturbed; the device is also unpowered</t>
           </r>
           <r>
             <rPr>
@@ -7528,60 +7476,60 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>D2 (car side, CAN0) or D3 (camera side, CAN2) shorts a CAN line to GND or VIN in either switch state</t>
-          </r>
-        </is>
-      </c>
-      <c r="D30" s="31" t="inlineStr">
+            <t>U1/U2 unpowered, so pass-through is not guaranteed; D2/D3 clamp CAN0 and CAN2 towards the dead VIN rail, which the device input loads (derived from the v3 drawing, to confirm on the bench)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
         <is>
           <t>HZ-011
 HZ-004</t>
         </is>
       </c>
-      <c r="E30" s="32" t="n">
+      <c r="E30" s="42" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001F4E8C"/>
-              <sz val="9"/>
-            </rPr>
-            <t xml:space="preserve">DFM-021 · short
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <b val="1"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Clamp diode short loads or grounds a vehicle bus in the harness box</t>
-          </r>
-        </is>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
+      <c r="F30" s="40" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-020 · loss
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Harness box loses its supply while the car is on</t>
+          </r>
+        </is>
+      </c>
+      <c r="G30" s="43" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
       </c>
-      <c r="H30" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <color rgb="001B2430"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Schottky clamp D2 or D3 (BAS40SDW) short or leaky</t>
-          </r>
-        </is>
-      </c>
-      <c r="I30" s="34" t="inlineStr">
+      <c r="H30" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Ignition branch to the box open (crimp, connector) or D1 open, without comma power installed</t>
+          </r>
+        </is>
+      </c>
+      <c r="I30" s="44" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7602,10 +7550,110 @@
           </r>
         </is>
       </c>
-      <c r="J30" s="35" t="n">
+      <c r="J30" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L30" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N30" s="44" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O30" s="48" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P30" s="43" t="inlineStr"/>
+      <c r="Q30" s="43" t="inlineStr"/>
+      <c r="R30" s="49" t="inlineStr"/>
+      <c r="S30" s="49" t="inlineStr"/>
+    </row>
+    <row r="31" ht="127.5" customHeight="1">
+      <c r="A31" s="50" t="n"/>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+      <c r="E31" s="50" t="n"/>
+      <c r="F31" s="50" t="n"/>
+      <c r="G31" s="33" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="H31" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Box VIN shorted to ground (TVS D4 short, connector or wiring)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I31" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J31" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="34" t="inlineStr">
+      <c r="K31" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7617,15 +7665,15 @@
           </r>
         </is>
       </c>
-      <c r="L30" s="36" t="n">
+      <c r="L31" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="M30" s="37" t="inlineStr">
+      <c r="M31" s="37" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N30" s="34" t="inlineStr">
+      <c r="N31" s="34" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7647,62 +7695,337 @@
           </r>
         </is>
       </c>
-      <c r="O30" s="38" t="inlineStr">
+      <c r="O31" s="38" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="P30" s="33" t="inlineStr"/>
-      <c r="Q30" s="33" t="inlineStr"/>
-      <c r="R30" s="39" t="inlineStr"/>
-      <c r="S30" s="39" t="inlineStr"/>
+      <c r="P31" s="33" t="inlineStr"/>
+      <c r="Q31" s="33" t="inlineStr"/>
+      <c r="R31" s="39" t="inlineStr"/>
+      <c r="S31" s="39" t="inlineStr"/>
+    </row>
+    <row r="32" ht="127.5" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Loss of lateral control with a late or no warning</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Car-side ADAS CAN or the camera bus cannot communicate; stock PCS messages lost</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>D2 (car side, CAN0) or D3 (camera side, CAN2) shorts a CAN line to GND or VIN in either switch state</t>
+          </r>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011
+HZ-004</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-021 · short
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Clamp diode short loads or grounds a vehicle bus in the harness box</t>
+          </r>
+        </is>
+      </c>
+      <c r="G32" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H32" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Schottky clamp D2 or D3 (BAS40SDW) short or leaky</t>
+          </r>
+        </is>
+      </c>
+      <c r="I32" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause (WP-H-06/WP-H-07 not started; no HIL bench, D-04)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L32" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N32" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          </r>
+        </is>
+      </c>
+      <c r="O32" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P32" s="33" t="inlineStr"/>
+      <c r="Q32" s="33" t="inlineStr"/>
+      <c r="R32" s="39" t="inlineStr"/>
+      <c r="S32" s="39" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:S30"/>
-  <mergeCells count="40">
+  <autoFilter ref="A2:S32"/>
+  <mergeCells count="46">
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E13:E16"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="C21:C22"/>
     <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B19:B20"/>
     <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A21:A22"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D13:D16"/>
+    <mergeCell ref="F13:F16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="C17:C18"/>
     <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="D25:D26"/>
     <mergeCell ref="I1:M1"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="A19:A20"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="B30:B31"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="D26:D27"/>
     <mergeCell ref="N1:Q1"/>
-    <mergeCell ref="B13:B15"/>
     <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B21:B22"/>
     <mergeCell ref="R1:S1"/>
+    <mergeCell ref="A30:A31"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7710,7 +8033,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.5 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.6 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7725,7 +8048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8253,7 +8576,7 @@
       <c r="H14" s="53" t="inlineStr"/>
       <c r="I14" s="53" t="inlineStr"/>
     </row>
-    <row r="15" ht="73.5" customHeight="1">
+    <row r="15" ht="100.5" customHeight="1">
       <c r="A15" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-014</t>
@@ -8282,6 +8605,8 @@
       <c r="F15" s="53" t="inlineStr">
         <is>
           <t>DFM-010.C3
+DFM-010.C4
+DFM-011.C2
 DFM-014.C2
 DFM-020.C1
 DFM-020.C2
@@ -8292,8 +8617,44 @@
       <c r="H15" s="53" t="inlineStr"/>
       <c r="I15" s="53" t="inlineStr"/>
     </row>
+    <row r="16" ht="100.5" customHeight="1">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
+          <t>DFM-ACT-015</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C16" s="53" t="inlineStr">
+        <is>
+          <t>Read the Vishay DG417LE/DG418LE/DG419LE datasheet (document 76432) and record the absolute maximum V+ to V-, VL and IN ratings, the single-supply operating range and VINH/VINL at VL = V+ = 14 V; compare with VIN including the D4 clamp level. If a limit is exceeded, raise it with comma.ai and with DQ-209 (RR-2026-010 F-05; blocked at 2026-10-16: vendor and datasheet hosts unreachable from the analysis environment)</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F16" s="53" t="inlineStr">
+        <is>
+          <t>DFM-010.C4
+DFM-011.C2</t>
+        </is>
+      </c>
+      <c r="G16" s="53" t="inlineStr"/>
+      <c r="H16" s="53" t="inlineStr"/>
+      <c r="I16" s="53" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I15"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -2445,7 +2445,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04)</t>
+            <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04). The lead deferred the HIL bench (DQ-049, 2026-10-14), so this waits for the bench</t>
           </r>
         </is>
       </c>
@@ -2991,7 +2991,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04)</t>
+            <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04). The lead deferred the HIL bench (DQ-049, 2026-10-14), so this waits for the bench</t>
           </r>
         </is>
       </c>
@@ -8181,7 +8181,7 @@
       <c r="H3" s="53" t="inlineStr"/>
       <c r="I3" s="53" t="inlineStr"/>
     </row>
-    <row r="4" ht="33" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-003</t>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C4" s="53" t="inlineStr">
         <is>
-          <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04)</t>
+          <t>Run the watchdog HIL test (test_10_hw_watchdog) on the bench and confirm the relay releases on reset (HWSR-502, UK-06) (D-04). The lead deferred the HIL bench (DQ-049, 2026-10-14), so this waits for the bench</t>
         </is>
       </c>
       <c r="D4" s="53" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.6 · draft</t>
+          <t>0.7 · draft</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-002</t>
+          <t>BL-005</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Safety-relevant hardware of AC-001 at BL-002: comma 3X panda section (STM32H725, clock and watchdog, MCU supply, CAN transceivers), Toyota harness and relay box, SoC-MCU interface, siren path, enclosure and cooling. SoC, cameras and other QM hardware only where they couple into these (WP-A-03).</t>
+          <t>Safety-relevant hardware of AC-001 at BL-005 (hardware as at BL-002): comma 3X panda section (STM32H725, clock and watchdog, MCU supply, CAN transceivers), Toyota harness and relay box, SoC-MCU interface, siren path, enclosure and cooling. SoC, cameras and other QM hardware only where they couple into these (WP-A-03).</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       <c r="R22" s="39" t="inlineStr"/>
       <c r="S22" s="39" t="inlineStr"/>
     </row>
-    <row r="23" ht="154.5" customHeight="1">
+    <row r="23" ht="168" customHeight="1">
       <c r="A23" s="30" t="inlineStr">
         <is>
           <r>
@@ -5913,7 +5913,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (reference build only)</t>
+            <t>• 8-bit XOR on header and data, NACK on mismatch (drivers/spi.h:97-138); reference lock limits what a corrupted 0xdc can select (default build from BL-005, LionDriver</t>
           </r>
           <r>
             <rPr>
@@ -8033,7 +8033,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.6 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.7 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -11,12 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worksheet" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -252,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -378,6 +381,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,7 +750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:C33"/>
+  <dimension ref="B2:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -914,104 +920,112 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>FMEA-MSR (msr: complete)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>19 rated, 0 exempt; MSR AP H 19, M 0, L 0 (provisional table)</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Monitoring M</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>1–4: 0 · 5–6: 0 · 7–8: 5 · 9–10: 14 (see sheet MSR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="12" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>High: an action or a rationale is required</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="14" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Medium: an action or a rationale is recommended</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="15" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="16" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Aa</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>Amber text: no test targets the cause (detection 9 or 10)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="17" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="17" t="inlineStr"/>
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>Yellow cells on the Worksheet: reviewer input (decision from the list, comment)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Review sign-off</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Independence level</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="18" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Reviewer</t>
         </is>
       </c>
       <c r="C31" s="19" t="inlineStr"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Result (accepted / accepted with findings / rejected)</t>
+          <t>Independence level</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr"/>
@@ -1019,10 +1033,26 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="18" t="inlineStr">
         <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Result (accepted / accepted with findings / rejected)</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="18" t="inlineStr">
+        <is>
           <t>Findings reference</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr"/>
+      <c r="C35" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8607,4 +8637,1337 @@
   <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="54" t="inlineStr">
+        <is>
+          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="28" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>Cause</t>
+        </is>
+      </c>
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>Failure cause</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>System response</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="inlineStr">
+        <is>
+          <t>Effect after the response</t>
+        </is>
+      </c>
+      <c r="H2" s="29" t="inlineStr">
+        <is>
+          <t>S after</t>
+        </is>
+      </c>
+      <c r="I2" s="29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J2" s="29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K2" s="29" t="inlineStr">
+        <is>
+          <t>MSR AP</t>
+        </is>
+      </c>
+      <c r="L2" s="28" t="inlineStr">
+        <is>
+          <t>Timing (FTTI · FDTI + FRTI)</t>
+        </is>
+      </c>
+      <c r="M2" s="29" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="N2" s="28" t="inlineStr">
+        <is>
+          <t>Monitoring actions</t>
+        </is>
+      </c>
+      <c r="O2" s="28" t="inlineStr">
+        <is>
+          <t>Reviewer decision</t>
+        </is>
+      </c>
+      <c r="P2" s="28" t="inlineStr">
+        <is>
+          <t>Reviewer comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46.5" customHeight="1">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>DFM-001 · Safety check computes a wrong result (permanent CPU or data-path fault)</t>
+        </is>
+      </c>
+      <c r="B3" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>DFM-001.C1</t>
+        </is>
+      </c>
+      <c r="D3" s="44" t="inlineStr">
+        <is>
+          <t>Permanent fault in the Cortex-M7 core or bus matrix; single core, no lockstep, no CPU self-test</t>
+        </is>
+      </c>
+      <c r="E3" s="44" t="inlineStr">
+        <is>
+          <t>None in the MCU at BL-002. The host compares controls_allowed after about 2 s (QM); it does not check limits</t>
+        </is>
+      </c>
+      <c r="F3" s="44" t="inlineStr">
+        <is>
+          <t>None for a wrong limit result</t>
+        </is>
+      </c>
+      <c r="G3" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: a wrong check result lets an over-limit or unauthorised frame through</t>
+        </is>
+      </c>
+      <c r="H3" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L3" s="44" t="inlineStr"/>
+      <c r="M3" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N3" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-001 · open</t>
+        </is>
+      </c>
+      <c r="O3" s="49" t="inlineStr"/>
+      <c r="P3" s="49" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>DFM-002 · Code or limit constants corrupted in flash during operation</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>DFM-002.C1</t>
+        </is>
+      </c>
+      <c r="D4" s="44" t="inlineStr">
+        <is>
+          <t>Multi-bit flash error or cell degradation; double-error ECC flag not handled; image signature checked at boot only</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="inlineStr">
+        <is>
+          <t>Bootstub signature check at power-up only; no periodic code CRC in the pinned firmware</t>
+        </is>
+      </c>
+      <c r="F4" s="44" t="inlineStr">
+        <is>
+          <t>None during the drive</t>
+        </is>
+      </c>
+      <c r="G4" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged until the next power-up</t>
+        </is>
+      </c>
+      <c r="H4" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L4" s="44" t="inlineStr"/>
+      <c r="M4" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N4" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-002 · open</t>
+        </is>
+      </c>
+      <c r="O4" s="49" t="inlineStr"/>
+      <c r="P4" s="49" t="inlineStr"/>
+    </row>
+    <row r="5" ht="46.5" customHeight="1">
+      <c r="A5" s="44" t="inlineStr">
+        <is>
+          <t>DFM-003 · Safety state in SRAM corrupted (controls_allowed, limits, counters, stack)</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>DFM-003.C1</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>Double-bit soft error or permanent SRAM fault; RAMECC monitors not configured, ECC interrupt not registered</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>None at BL-002: RAMECC monitors not configured, no redundant storage</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H5" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L5" s="44" t="inlineStr"/>
+      <c r="M5" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N5" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-002 · open</t>
+        </is>
+      </c>
+      <c r="O5" s="49" t="inlineStr"/>
+      <c r="P5" s="49" t="inlineStr"/>
+    </row>
+    <row r="6" ht="46.5" customHeight="1">
+      <c r="A6" s="44" t="inlineStr">
+        <is>
+          <t>DFM-003 · Safety state in SRAM corrupted (controls_allowed, limits, counters, stack)</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>DFM-003.C2</t>
+        </is>
+      </c>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Wrong-address write by the SPI DMA (no MPU)</t>
+        </is>
+      </c>
+      <c r="E6" s="44" t="inlineStr">
+        <is>
+          <t>None at BL-002: no MPU and no redundant storage of the safety state</t>
+        </is>
+      </c>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H6" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L6" s="44" t="inlineStr"/>
+      <c r="M6" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N6" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-002 · open</t>
+        </is>
+      </c>
+      <c r="O6" s="49" t="inlineStr"/>
+      <c r="P6" s="49" t="inlineStr"/>
+    </row>
+    <row r="7" ht="73.5" customHeight="1">
+      <c r="A7" s="44" t="inlineStr">
+        <is>
+          <t>DFM-004 · MCU execution stops with the relay energised</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>DFM-004.C1</t>
+        </is>
+      </c>
+      <c r="D7" s="44" t="inlineStr">
+        <is>
+          <t>Hang in an ISR or main loop, unused vector to Default_Handler, or assert_fatal loop</t>
+        </is>
+      </c>
+      <c r="E7" s="44" t="inlineStr">
+        <is>
+          <t>IWDG expires about 90 ms after the last feed (T-09a). Timing fits on paper, but whether the reset releases the relay is unconfirmed (HWSR-502, UK-06) and the LSI tolerance leaves no shown margin (OI-7), so the response is not credited</t>
+        </is>
+      </c>
+      <c r="F7" s="44" t="inlineStr">
+        <is>
+          <t>MCU reset; relay de-energised if the drive circuit is de-energise-to-safe; stock camera CAN restored</t>
+        </is>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>Stock PCS/AEB restored and assist lost, if the relay releases</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="45" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="45" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L7" s="44" t="inlineStr">
+        <is>
+          <t>SG-07 forwarding loss · 200 ms
+90 + 100 ms</t>
+        </is>
+      </c>
+      <c r="M7" s="43" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N7" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-003 · open</t>
+        </is>
+      </c>
+      <c r="O7" s="49" t="inlineStr"/>
+      <c r="P7" s="49" t="inlineStr"/>
+    </row>
+    <row r="8" ht="46.5" customHeight="1">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>DFM-007 · MCU operates in the brown-out zone</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>DFM-007.C1</t>
+        </is>
+      </c>
+      <c r="D8" s="44" t="inlineStr">
+        <is>
+          <t>Vehicle supply dip (cranking, alternator fault) with BOR level not set and PVD not enabled</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="inlineStr">
+        <is>
+          <t>None at BL-002: PVD handler is a stub and the BOR level is unknown (UK-04)</t>
+        </is>
+      </c>
+      <c r="F8" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: erratic MCU behaviour in the brown-out zone</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L8" s="44" t="inlineStr"/>
+      <c r="M8" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N8" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-005 · open</t>
+        </is>
+      </c>
+      <c r="O8" s="49" t="inlineStr"/>
+      <c r="P8" s="49" t="inlineStr"/>
+    </row>
+    <row r="9" ht="46.5" customHeight="1">
+      <c r="A9" s="44" t="inlineStr">
+        <is>
+          <t>DFM-008 · Car-side transceiver holds the bus dominant</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>DFM-008.C1</t>
+        </is>
+      </c>
+      <c r="D9" s="44" t="inlineStr">
+        <is>
+          <t>XCVR1 TX driver fault or TXD stuck low</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>FDCAN error counters; core reset on bus-off. The transceiver dominant timeout is part dependent and unknown</t>
+        </is>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>A core reset does not release a transceiver that holds the bus dominant; no safe-state reaction</t>
+        </is>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>Car bus blocked: loss of assist and of stock CAN functions until the transceiver times out, if it does</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L9" s="44" t="inlineStr"/>
+      <c r="M9" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N9" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-006 · open</t>
+        </is>
+      </c>
+      <c r="O9" s="49" t="inlineStr"/>
+      <c r="P9" s="49" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46.5" customHeight="1">
+      <c r="A10" s="44" t="inlineStr">
+        <is>
+          <t>DFM-009 · Car-side transceiver receives nothing</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>DFM-009.C1</t>
+        </is>
+      </c>
+      <c r="D10" s="44" t="inlineStr">
+        <is>
+          <t>XCVR1 RX open or stuck recessive</t>
+        </is>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>RX timeout after 5 periods (about 0.16 s) withdraws controls_allowed; the host warns through the 2 s controlsMismatch counter (T-17)</t>
+        </is>
+      </c>
+      <c r="F10" s="44" t="inlineStr">
+        <is>
+          <t>Authority withdrawn at once; warning about 2.2 s after onset, beyond the 1 s budget to warning</t>
+        </is>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>Assist lost; warning late</t>
+        </is>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L10" s="44" t="inlineStr">
+        <is>
+          <t>SG-02/06 loss without warning · 1000 ms
+160 + 2000 ms</t>
+        </is>
+      </c>
+      <c r="M10" s="43" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N10" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-006 · open</t>
+        </is>
+      </c>
+      <c r="O10" s="49" t="inlineStr"/>
+      <c r="P10" s="49" t="inlineStr"/>
+    </row>
+    <row r="11" ht="46.5" customHeight="1">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>DFM-010 · Intercept switch stays in intercept when released</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>DFM-010.C1</t>
+        </is>
+      </c>
+      <c r="D11" s="44" t="inlineStr">
+        <is>
+          <t>Analog switch U1 or U2 stuck in the intercept (NO) position, or its IN input damaged high</t>
+        </is>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>None: no relay readback (GAP-12)</t>
+        </is>
+      </c>
+      <c r="F11" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: stock camera stays cut off after release is commanded</t>
+        </is>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L11" s="44" t="inlineStr"/>
+      <c r="M11" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N11" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O11" s="49" t="inlineStr"/>
+      <c r="P11" s="49" t="inlineStr"/>
+    </row>
+    <row r="12" ht="46.5" customHeight="1">
+      <c r="A12" s="44" t="inlineStr">
+        <is>
+          <t>DFM-010 · Intercept switch stays in intercept when released</t>
+        </is>
+      </c>
+      <c r="B12" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>DFM-010.C2</t>
+        </is>
+      </c>
+      <c r="D12" s="44" t="inlineStr">
+        <is>
+          <t>SBU1 drive stuck high (device-side driver or MCU pin, UK-06)</t>
+        </is>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>None: no relay readback (GAP-12)</t>
+        </is>
+      </c>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: stock camera stays cut off after release is commanded</t>
+        </is>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L12" s="44" t="inlineStr"/>
+      <c r="M12" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N12" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O12" s="49" t="inlineStr"/>
+      <c r="P12" s="49" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>DFM-010 · Intercept switch stays in intercept when released</t>
+        </is>
+      </c>
+      <c r="B13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>DFM-010.C3</t>
+        </is>
+      </c>
+      <c r="D13" s="44" t="inlineStr">
+        <is>
+          <t>Pull-down R2 or R3 open, so IN floats when the device stops driving SBU1 (reset, watchdog, hang, unplugged cable)</t>
+        </is>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>None: the open pull-down is latent while the device drives SBU1, and no readback exists (GAP-12)</t>
+        </is>
+      </c>
+      <c r="F13" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: the switch may stay in intercept with the device silent, so the stock camera stays cut off</t>
+        </is>
+      </c>
+      <c r="H13" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L13" s="44" t="inlineStr"/>
+      <c r="M13" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N13" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-007 · open
+DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O13" s="49" t="inlineStr"/>
+      <c r="P13" s="49" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>DFM-011 · Intercept switch stays in pass-through when driven</t>
+        </is>
+      </c>
+      <c r="B14" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>DFM-011.C1</t>
+        </is>
+      </c>
+      <c r="D14" s="44" t="inlineStr">
+        <is>
+          <t>Analog switch U1 or U2 stuck in the pass-through (NC) position, or SBU1 drive lost or held low (driver open, R2/R3 short)</t>
+        </is>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Relay malfunction: a stock camera frame on the car side after the 1 s grace blocks all TX (T-08, 1-2 s)</t>
+        </is>
+      </c>
+      <c r="F14" s="44" t="inlineStr">
+        <is>
+          <t>All TX blocked; host raises relayMalfunction (IMMEDIATE_DISABLE)</t>
+        </is>
+      </c>
+      <c r="G14" s="44" t="inlineStr">
+        <is>
+          <t>Up to 2 s of stock LKA and item commands on the bus together, then no item output</t>
+        </is>
+      </c>
+      <c r="H14" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L14" s="44" t="inlineStr">
+        <is>
+          <t>SG-01 relay stuck · 500 ms
+2000 + 10 ms</t>
+        </is>
+      </c>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>code derived</t>
+        </is>
+      </c>
+      <c r="N14" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-007 · open</t>
+        </is>
+      </c>
+      <c r="O14" s="49" t="inlineStr"/>
+      <c r="P14" s="49" t="inlineStr"/>
+    </row>
+    <row r="15" ht="46.5" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>DFM-012 · Harness disconnected or intermittent while driving</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>DFM-012.C1</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>Connector not fully latched at installation, or vibration loosens it</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>RX timeouts and host canBusMissing cover a partial disconnect only; a full disconnect also removes the device supply, so nothing warns</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>Relay drops out with the supply; stock camera restored</t>
+        </is>
+      </c>
+      <c r="G15" s="44" t="inlineStr">
+        <is>
+          <t>Assist lost without a LionDriver warning</t>
+        </is>
+      </c>
+      <c r="H15" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L15" s="44" t="inlineStr"/>
+      <c r="M15" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N15" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-008 · open</t>
+        </is>
+      </c>
+      <c r="O15" s="49" t="inlineStr"/>
+      <c r="P15" s="49" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>DFM-016 · MCU forced into the ROM bootloader or reflashed by the SoC</t>
+        </is>
+      </c>
+      <c r="B16" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>DFM-016.C1</t>
+        </is>
+      </c>
+      <c r="D16" s="44" t="inlineStr">
+        <is>
+          <t>SoC drives STM_BOOT0/STM_RST_N (fault or compromise); no RDP/WRP; pandad recovery flashes a development bootstub</t>
+        </is>
+      </c>
+      <c r="E16" s="44" t="inlineStr">
+        <is>
+          <t>Bootstub signature check exists but accepts the debug key in debug builds; RDP and WRP not set (GAP-24)</t>
+        </is>
+      </c>
+      <c r="F16" s="44" t="inlineStr">
+        <is>
+          <t>None for a signed debug image</t>
+        </is>
+      </c>
+      <c r="G16" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H16" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="K16" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L16" s="44" t="inlineStr"/>
+      <c r="M16" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N16" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-010 · open</t>
+        </is>
+      </c>
+      <c r="O16" s="49" t="inlineStr"/>
+      <c r="P16" s="49" t="inlineStr"/>
+    </row>
+    <row r="17" ht="100.5" customHeight="1">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>DFM-019 · Approved CAN frame altered between the TX check and the bus</t>
+        </is>
+      </c>
+      <c r="B17" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>DFM-019.C1</t>
+        </is>
+      </c>
+      <c r="D17" s="44" t="inlineStr">
+        <is>
+          <t>Soft error or permanent fault in the copy into FDCAN message RAM, the message RAM or the FDCAN core. The packet XOR is checked at the FDCAN load (fdcan.h:100) and covers only the software queue; the CAN CRC is computed after the fault</t>
+        </is>
+      </c>
+      <c r="E17" s="44" t="inlineStr">
+        <is>
+          <t>None after the FDCAN load: no TX read-back (TSR-517 not implemented)</t>
+        </is>
+      </c>
+      <c r="F17" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G17" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H17" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L17" s="44" t="inlineStr"/>
+      <c r="M17" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N17" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-013 · open</t>
+        </is>
+      </c>
+      <c r="O17" s="49" t="inlineStr"/>
+      <c r="P17" s="49" t="inlineStr"/>
+    </row>
+    <row r="18" ht="100.5" customHeight="1">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>DFM-019 · Approved CAN frame altered between the TX check and the bus</t>
+        </is>
+      </c>
+      <c r="B18" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>DFM-019.C2</t>
+        </is>
+      </c>
+      <c r="D18" s="44" t="inlineStr">
+        <is>
+          <t>Transceiver fault that changes bits on TX without a CAN error (not credible for a single bit, which the CAN CRC and the bit monitoring of the transmitting controller detect; kept until the transceiver part is known, WP-H-02 UK-01)</t>
+        </is>
+      </c>
+      <c r="E18" s="44" t="inlineStr">
+        <is>
+          <t>None: no TX read-back (TSR-517 not implemented)</t>
+        </is>
+      </c>
+      <c r="F18" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G18" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H18" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L18" s="44" t="inlineStr"/>
+      <c r="M18" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N18" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-013 · open</t>
+        </is>
+      </c>
+      <c r="O18" s="49" t="inlineStr"/>
+      <c r="P18" s="49" t="inlineStr"/>
+    </row>
+    <row r="19" ht="46.5" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>DFM-020 · Harness box loses its supply while the car is on</t>
+        </is>
+      </c>
+      <c r="B19" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>DFM-020.C1</t>
+        </is>
+      </c>
+      <c r="D19" s="44" t="inlineStr">
+        <is>
+          <t>Ignition branch to the box open (crimp, connector) or D1 open, without comma power installed</t>
+        </is>
+      </c>
+      <c r="E19" s="44" t="inlineStr">
+        <is>
+          <t>None: the box supply is not supervised, and the device loses power with it</t>
+        </is>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G19" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H19" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L19" s="44" t="inlineStr"/>
+      <c r="M19" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N19" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr"/>
+      <c r="P19" s="49" t="inlineStr"/>
+    </row>
+    <row r="20" ht="33" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>DFM-020 · Harness box loses its supply while the car is on</t>
+        </is>
+      </c>
+      <c r="B20" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>DFM-020.C2</t>
+        </is>
+      </c>
+      <c r="D20" s="44" t="inlineStr">
+        <is>
+          <t>Box VIN shorted to ground (TVS D4 short, connector or wiring)</t>
+        </is>
+      </c>
+      <c r="E20" s="44" t="inlineStr">
+        <is>
+          <t>None: the box supply is not supervised, and the device loses power with it</t>
+        </is>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G20" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged</t>
+        </is>
+      </c>
+      <c r="H20" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L20" s="44" t="inlineStr"/>
+      <c r="M20" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N20" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O20" s="49" t="inlineStr"/>
+      <c r="P20" s="49" t="inlineStr"/>
+    </row>
+    <row r="21" ht="46.5" customHeight="1">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>DFM-021 · Clamp diode short loads or grounds a vehicle bus in the harness box</t>
+        </is>
+      </c>
+      <c r="B21" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>DFM-021.C1</t>
+        </is>
+      </c>
+      <c r="D21" s="44" t="inlineStr">
+        <is>
+          <t>Schottky clamp D2 or D3 (BAS40SDW) short or leaky</t>
+        </is>
+      </c>
+      <c r="E21" s="44" t="inlineStr">
+        <is>
+          <t>RX timeouts withdraw control and the host raises CAN errors; nothing restores the bus</t>
+        </is>
+      </c>
+      <c r="F21" s="44" t="inlineStr">
+        <is>
+          <t>Authority withdrawn and the driver warned; the stock camera path stays broken</t>
+        </is>
+      </c>
+      <c r="G21" s="44" t="inlineStr">
+        <is>
+          <t>Item disengaged, but stock AEB stays unavailable</t>
+        </is>
+      </c>
+      <c r="H21" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="45" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L21" s="44" t="inlineStr"/>
+      <c r="M21" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N21" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O21" s="49" t="inlineStr"/>
+      <c r="P21" s="49" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P21"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+      <formula1>"Agree,Re-rate,Reject,Question"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.5 · BL-002&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -3794,7 +3794,7 @@
       <c r="R12" s="39" t="inlineStr"/>
       <c r="S12" s="39" t="inlineStr"/>
     </row>
-    <row r="13" ht="87" customHeight="1">
+    <row r="13" ht="127.5" customHeight="1">
       <c r="A13" s="40" t="inlineStr">
         <is>
           <r>
@@ -4022,13 +4022,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03). Not implemented by decision DQ-209 option A (2026-10-16): comma's box is kept and its failure behaviour is bench-tested (DFM-ACT-014) and argued as residual risk; the de-energised state is covered by DFM-ACT-014</t>
           </r>
         </is>
       </c>
       <c r="O13" s="48" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not implemented</t>
         </is>
       </c>
       <c r="P13" s="43" t="inlineStr"/>
@@ -4036,7 +4036,7 @@
       <c r="R13" s="49" t="inlineStr"/>
       <c r="S13" s="49" t="inlineStr"/>
     </row>
-    <row r="14" ht="87" customHeight="1">
+    <row r="14" ht="127.5" customHeight="1">
       <c r="A14" s="51" t="n"/>
       <c r="B14" s="51" t="n"/>
       <c r="C14" s="51" t="n"/>
@@ -4122,13 +4122,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03). Not implemented by decision DQ-209 option A (2026-10-16): comma's box is kept and its failure behaviour is bench-tested (DFM-ACT-014) and argued as residual risk; the de-energised state is covered by DFM-ACT-014</t>
           </r>
         </is>
       </c>
       <c r="O14" s="48" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not implemented</t>
         </is>
       </c>
       <c r="P14" s="43" t="inlineStr"/>
@@ -4136,7 +4136,7 @@
       <c r="R14" s="49" t="inlineStr"/>
       <c r="S14" s="49" t="inlineStr"/>
     </row>
-    <row r="15" ht="181.5" customHeight="1">
+    <row r="15" ht="276" customHeight="1">
       <c r="A15" s="51" t="n"/>
       <c r="B15" s="51" t="n"/>
       <c r="C15" s="51" t="n"/>
@@ -4222,7 +4222,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03). Not implemented by decision DQ-209 option A (2026-10-16): comma's box is kept and its failure behaviour is bench-tested (DFM-ACT-014) and argued as residual risk; the de-energised state is covered by DFM-ACT-014</t>
           </r>
           <r>
             <rPr>
@@ -4249,13 +4249,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
       <c r="O15" s="48" t="inlineStr">
         <is>
-          <t>open
+          <t>not implemented
 open</t>
         </is>
       </c>
@@ -4264,7 +4264,7 @@
       <c r="R15" s="49" t="inlineStr"/>
       <c r="S15" s="49" t="inlineStr"/>
     </row>
-    <row r="16" ht="276" customHeight="1">
+    <row r="16" ht="303" customHeight="1">
       <c r="A16" s="50" t="n"/>
       <c r="B16" s="50" t="n"/>
       <c r="C16" s="50" t="n"/>
@@ -4376,7 +4376,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
           <r>
             <rPr>
@@ -4418,7 +4418,7 @@
       <c r="R16" s="39" t="inlineStr"/>
       <c r="S16" s="39" t="inlineStr"/>
     </row>
-    <row r="17" ht="87" customHeight="1">
+    <row r="17" ht="127.5" customHeight="1">
       <c r="A17" s="40" t="inlineStr">
         <is>
           <r>
@@ -4682,13 +4682,13 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+            <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03). Not implemented by decision DQ-209 option A (2026-10-16): comma's box is kept and its failure behaviour is bench-tested (DFM-ACT-014) and argued as residual risk; the de-energised state is covered by DFM-ACT-014</t>
           </r>
         </is>
       </c>
       <c r="O17" s="48" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not implemented</t>
         </is>
       </c>
       <c r="P17" s="43" t="inlineStr"/>
@@ -4696,7 +4696,7 @@
       <c r="R17" s="49" t="inlineStr"/>
       <c r="S17" s="49" t="inlineStr"/>
     </row>
-    <row r="18" ht="276" customHeight="1">
+    <row r="18" ht="303" customHeight="1">
       <c r="A18" s="50" t="n"/>
       <c r="B18" s="50" t="n"/>
       <c r="C18" s="50" t="n"/>
@@ -4817,7 +4817,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
           <r>
             <rPr>
@@ -5585,7 +5585,7 @@
       <c r="R21" s="49" t="inlineStr"/>
       <c r="S21" s="49" t="inlineStr"/>
     </row>
-    <row r="22" ht="181.5" customHeight="1">
+    <row r="22" ht="208.5" customHeight="1">
       <c r="A22" s="50" t="n"/>
       <c r="B22" s="50" t="n"/>
       <c r="C22" s="50" t="n"/>
@@ -5698,7 +5698,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7336,7 +7336,7 @@
       <c r="R29" s="39" t="inlineStr"/>
       <c r="S29" s="39" t="inlineStr"/>
     </row>
-    <row r="30" ht="127.5" customHeight="1">
+    <row r="30" ht="154.5" customHeight="1">
       <c r="A30" s="40" t="inlineStr">
         <is>
           <r>
@@ -7591,7 +7591,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7605,7 +7605,7 @@
       <c r="R30" s="49" t="inlineStr"/>
       <c r="S30" s="49" t="inlineStr"/>
     </row>
-    <row r="31" ht="127.5" customHeight="1">
+    <row r="31" ht="154.5" customHeight="1">
       <c r="A31" s="50" t="n"/>
       <c r="B31" s="50" t="n"/>
       <c r="C31" s="50" t="n"/>
@@ -7691,7 +7691,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7705,7 +7705,7 @@
       <c r="R31" s="39" t="inlineStr"/>
       <c r="S31" s="39" t="inlineStr"/>
     </row>
-    <row r="32" ht="127.5" customHeight="1">
+    <row r="32" ht="154.5" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
           <r>
@@ -7960,7 +7960,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -8323,7 +8323,7 @@
       <c r="H7" s="53" t="inlineStr"/>
       <c r="I7" s="53" t="inlineStr"/>
     </row>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="73.5" customHeight="1">
       <c r="A8" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-007</t>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="C8" s="53" t="inlineStr">
         <is>
-          <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03)</t>
+          <t>Add relay readback in a LionDriver harness adapter (WP-H-02 DC-03) and confirm the de-energised contact state (UK-03). Not implemented by decision DQ-209 option A (2026-10-16): comma's box is kept and its failure behaviour is bench-tested (DFM-ACT-014) and argued as residual risk; the de-energised state is covered by DFM-ACT-014</t>
         </is>
       </c>
       <c r="D8" s="53" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="E8" s="53" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not implemented</t>
         </is>
       </c>
       <c r="F8" s="53" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="C15" s="53" t="inlineStr">
         <is>
-          <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02)</t>
+          <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
         </is>
       </c>
       <c r="D15" s="53" t="inlineStr">

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$25</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
@@ -787,7 +787,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.7 · draft</t>
+          <t>0.8 · draft</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>15 (15)</t>
+          <t>16 (16)</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       <c r="R24" s="39" t="inlineStr"/>
       <c r="S24" s="39" t="inlineStr"/>
     </row>
-    <row r="25" ht="87" customHeight="1">
+    <row r="25" ht="208.5" customHeight="1">
       <c r="A25" s="40" t="inlineStr">
         <is>
           <r>
@@ -6537,11 +6537,39 @@
             </rPr>
             <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-016 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Time the EPS-fault warning chain on the HIL bench (WP-S-04 T-28): inject a persistent LKA_STATE fault on 0x262 while authority is granted and measure fault onset to audible siren against the 0.96 s design worst case and the SG-02 1 s budget (margin 0.04 s), with the speaker phase varied. Persistence 0.7 s since panda bf8102a (DQ-048). Waits for the HIL bench, which the lead deferred (DQ-049, 2026-10-14)</t>
+          </r>
         </is>
       </c>
       <c r="O25" s="48" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P25" s="43" t="inlineStr"/>
@@ -6549,7 +6577,7 @@
       <c r="R25" s="49" t="inlineStr"/>
       <c r="S25" s="49" t="inlineStr"/>
     </row>
-    <row r="26" ht="87" customHeight="1">
+    <row r="26" ht="208.5" customHeight="1">
       <c r="A26" s="50" t="n"/>
       <c r="B26" s="50" t="n"/>
       <c r="C26" s="50" t="n"/>
@@ -6637,11 +6665,39 @@
             </rPr>
             <t>Confirm the siren audio topology (UK-07) and add a start-up siren self-test (TSR-515/516)</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-016 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Time the EPS-fault warning chain on the HIL bench (WP-S-04 T-28): inject a persistent LKA_STATE fault on 0x262 while authority is granted and measure fault onset to audible siren against the 0.96 s design worst case and the SG-02 1 s budget (margin 0.04 s), with the speaker phase varied. Persistence 0.7 s since panda bf8102a (DQ-048). Waits for the HIL bench, which the lead deferred (DQ-049, 2026-10-14)</t>
+          </r>
         </is>
       </c>
       <c r="O26" s="38" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>open
+open</t>
         </is>
       </c>
       <c r="P26" s="33" t="inlineStr"/>
@@ -8063,7 +8119,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.7 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.8 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8078,7 +8134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8683,8 +8739,44 @@
       <c r="H16" s="53" t="inlineStr"/>
       <c r="I16" s="53" t="inlineStr"/>
     </row>
+    <row r="17" ht="87" customHeight="1">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>DFM-ACT-016</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>detection</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>Time the EPS-fault warning chain on the HIL bench (WP-S-04 T-28): inject a persistent LKA_STATE fault on 0x262 while authority is granted and measure fault onset to audible siren against the 0.96 s design worst case and the SG-02 1 s budget (margin 0.04 s), with the speaker phase varied. Persistence 0.7 s since panda bf8102a (DQ-048). Waits for the HIL bench, which the lead deferred (DQ-049, 2026-10-14)</t>
+        </is>
+      </c>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>Jherrod Thomas</t>
+        </is>
+      </c>
+      <c r="E17" s="53" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="inlineStr">
+        <is>
+          <t>DFM-017.C1
+DFM-017.C2</t>
+        </is>
+      </c>
+      <c r="G17" s="53" t="inlineStr"/>
+      <c r="H17" s="53" t="inlineStr"/>
+      <c r="I17" s="53" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I16"/>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10187,7 +10279,8 @@
       </c>
       <c r="N19" s="44" t="inlineStr">
         <is>
-          <t>DFM-ACT-011 · open</t>
+          <t>DFM-ACT-011 · open
+DFM-ACT-016 · open</t>
         </is>
       </c>
       <c r="O19" s="49" t="inlineStr"/>
@@ -10249,7 +10342,8 @@
       </c>
       <c r="N20" s="44" t="inlineStr">
         <is>
-          <t>DFM-ACT-011 · open</t>
+          <t>DFM-ACT-011 · open
+DFM-ACT-016 · open</t>
         </is>
       </c>
       <c r="O20" s="49" t="inlineStr"/>
@@ -10579,7 +10673,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.7 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.8 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.8 · draft</t>
+          <t>0.9 · draft</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Add a CPU self-test (vendor STL if available for STM32H7) at start-up and periodically, or argue the ASIL B target without CPU coverage (WP-H-03 finding 4)</t>
+            <t>Add a LionDriver CPU self-test at start-up and periodically (WP-H-03 finding 4). No vendor self-test library is licensed (decision DQ-069 option B, 2026-10-19), so CPU coverage is claimed only as low and the ASIL C SPFM target is likely missed (WP-H-04 OI-6, G2)</t>
           </r>
         </is>
       </c>
@@ -8119,7 +8119,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.8 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="46.5" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-001</t>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C2" s="53" t="inlineStr">
         <is>
-          <t>Add a CPU self-test (vendor STL if available for STM32H7) at start-up and periodically, or argue the ASIL B target without CPU coverage (WP-H-03 finding 4)</t>
+          <t>Add a LionDriver CPU self-test at start-up and periodically (WP-H-03 finding 4). No vendor self-test library is licensed (decision DQ-069 option B, 2026-10-19), so CPU coverage is claimed only as low and the ASIL C SPFM target is likely missed (WP-H-04 OI-6, G2)</t>
         </is>
       </c>
       <c r="D2" s="53" t="inlineStr">
@@ -10673,7 +10673,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.8 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -255,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -384,6 +384,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -787,7 +790,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.9 · draft</t>
+          <t>0.10 · draft</t>
         </is>
       </c>
     </row>
@@ -811,7 +814,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>RT-2</t>
+          <t>RT-3</t>
         </is>
       </c>
     </row>
@@ -928,7 +931,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>23 rated, 0 exempt; MSR AP H 23, M 0, L 0 (provisional table)</t>
+          <t>23 rated, 0 exempt; MSR AP H 20, M 3, L 0</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8122,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -9122,7 +9125,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="54" t="inlineStr">
         <is>
-          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-2). The MSR AP table is provisional until the handbook table is transcribed (decision register DQ-207). Exempt causes are rated in the FMEA named in the reason.</t>
+          <t>FMEA-MSR (monitoring and system response, msr-plan.md): S, F, M and MSR AP per rating-tables.md §7 (RT-3, handbook MSR AP table for S 9–10). Exempt causes are rated in the FMEA named in the reason.</t>
         </is>
       </c>
     </row>
@@ -9881,9 +9884,9 @@
       <c r="J13" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="K13" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="K13" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="L13" s="44" t="inlineStr"/>
@@ -10074,9 +10077,9 @@
       <c r="J16" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="K16" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="K16" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="L16" s="44" t="inlineStr">
@@ -10454,9 +10457,9 @@
       <c r="J22" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="K22" s="47" t="inlineStr">
-        <is>
-          <t>H</t>
+      <c r="K22" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
         </is>
       </c>
       <c r="L22" s="44" t="inlineStr"/>
@@ -10673,7 +10676,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.9 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.10 · draft</t>
+          <t>0.11 · draft</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BL-005</t>
+          <t>BL-007</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Safety-relevant hardware of AC-001 at BL-005 (hardware as at BL-002): comma 3X panda section (STM32H725, clock and watchdog, MCU supply, CAN transceivers), Toyota harness and relay box, SoC-MCU interface, siren path, enclosure and cooling. SoC, cameras and other QM hardware only where they couple into these (WP-A-03).</t>
+          <t>Safety-relevant hardware of AC-001 at BL-007 (hardware as at BL-002): comma 3X panda section (STM32H725, clock and watchdog, MCU supply, CAN transceivers), Toyota harness and relay box, SoC-MCU interface, siren path, enclosure and cooling. SoC, cameras and other QM hardware only where they couple into these (WP-A-03).</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10676,7 +10676,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.10 · BL-005&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.11 · draft</t>
+          <t>0.12 · draft</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8122,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10676,7 +10676,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.11 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
+++ b/assurance/08-analyses/fmea/exports/review/dfmea-review.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Worksheet'!$A$2:$S$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Worksheet'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actions'!$A$1:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Structure'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MSR'!$A$2:$P$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'MSR'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>0.12 · draft</t>
+          <t>0.13 · draft</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -931,7 +931,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>23 rated, 0 exempt; MSR AP H 20, M 3, L 0</t>
+          <t>25 rated, 0 exempt; MSR AP H 21, M 4, L 0</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>1–4: 0 · 5–6: 1 · 7–8: 5 · 9–10: 17 (see sheet MSR)</t>
+          <t>1–4: 0 · 5–6: 1 · 7–8: 5 · 9–10: 19 (see sheet MSR)</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4169,7 +4169,7 @@
       <c r="R14" s="49" t="inlineStr"/>
       <c r="S14" s="49" t="inlineStr"/>
     </row>
-    <row r="15" ht="276" customHeight="1">
+    <row r="15" ht="303" customHeight="1">
       <c r="A15" s="51" t="n"/>
       <c r="B15" s="51" t="n"/>
       <c r="C15" s="51" t="n"/>
@@ -4282,7 +4282,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="R15" s="49" t="inlineStr"/>
       <c r="S15" s="49" t="inlineStr"/>
     </row>
-    <row r="16" ht="303" customHeight="1">
+    <row r="16" ht="330" customHeight="1">
       <c r="A16" s="50" t="n"/>
       <c r="B16" s="50" t="n"/>
       <c r="C16" s="50" t="n"/>
@@ -4409,7 +4409,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
           <r>
             <rPr>
@@ -4729,7 +4729,7 @@
       <c r="R17" s="49" t="inlineStr"/>
       <c r="S17" s="49" t="inlineStr"/>
     </row>
-    <row r="18" ht="303" customHeight="1">
+    <row r="18" ht="330" customHeight="1">
       <c r="A18" s="50" t="n"/>
       <c r="B18" s="50" t="n"/>
       <c r="C18" s="50" t="n"/>
@@ -4850,7 +4850,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
           <r>
             <rPr>
@@ -5618,7 +5618,7 @@
       <c r="R21" s="49" t="inlineStr"/>
       <c r="S21" s="49" t="inlineStr"/>
     </row>
-    <row r="22" ht="208.5" customHeight="1">
+    <row r="22" ht="235.5" customHeight="1">
       <c r="A22" s="50" t="n"/>
       <c r="B22" s="50" t="n"/>
       <c r="C22" s="50" t="n"/>
@@ -5731,7 +5731,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7425,7 +7425,7 @@
       <c r="R29" s="39" t="inlineStr"/>
       <c r="S29" s="39" t="inlineStr"/>
     </row>
-    <row r="30" ht="154.5" customHeight="1">
+    <row r="30" ht="181.5" customHeight="1">
       <c r="A30" s="40" t="inlineStr">
         <is>
           <r>
@@ -7680,7 +7680,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7694,7 +7694,7 @@
       <c r="R30" s="49" t="inlineStr"/>
       <c r="S30" s="49" t="inlineStr"/>
     </row>
-    <row r="31" ht="154.5" customHeight="1">
+    <row r="31" ht="181.5" customHeight="1">
       <c r="A31" s="50" t="n"/>
       <c r="B31" s="50" t="n"/>
       <c r="C31" s="50" t="n"/>
@@ -7780,7 +7780,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -7794,7 +7794,7 @@
       <c r="R31" s="39" t="inlineStr"/>
       <c r="S31" s="39" t="inlineStr"/>
     </row>
-    <row r="32" ht="154.5" customHeight="1">
+    <row r="32" ht="181.5" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
           <r>
@@ -8049,7 +8049,7 @@
               <color rgb="001B2430"/>
               <sz val="10"/>
             </rPr>
-            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
           </r>
         </is>
       </c>
@@ -8063,8 +8063,501 @@
       <c r="R32" s="39" t="inlineStr"/>
       <c r="S32" s="39" t="inlineStr"/>
     </row>
+    <row r="33" ht="181.5" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera frames lost or corrupted while the device forwards them, so stock PCS messages do not reach the car</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>In intercept only the box terminates the camera bus (R7, and R8 through the harness P13-P15 loopback, 60 ohm). With both gone the recessive edge slows to about 10.5 us and misses the 1.5 us sample point (harness box SPICE pilot, a prediction)</t>
+          </r>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-022 · open
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera bus left unterminated in intercept</t>
+          </r>
+        </is>
+      </c>
+      <c r="G33" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H33" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Termination resistor R7 open together with R8 or the P13-P15 loopback open. One open alone leaves 120 ohm and a recessive edge of about 0.06 us, so it is latent (FMEDA SG-009 FMD-035); pass-through is not affected (R7/R8 are on the NO side)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I33" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J33" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware test has been run for this cause. Bench step VS-HW-24 (e) lifts R7, R8, then both, in intercept and records error frames and the recessive edge (WP-H-06 v0.13); not yet run</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-06-hardware-integration-verification.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="L33" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N33" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+          </r>
+        </is>
+      </c>
+      <c r="O33" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P33" s="33" t="inlineStr"/>
+      <c r="Q33" s="33" t="inlineStr"/>
+      <c r="R33" s="39" t="inlineStr"/>
+      <c r="S33" s="39" t="inlineStr"/>
+    </row>
+    <row r="34" ht="181.5" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-SE-006
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Intercept switch (harness box U1/U2) and its drive</t>
+          </r>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-FN-005
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Separate the camera from the car bus only while energised; restore the stock camera path whenever de-energised</t>
+          </r>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">End  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Stock AEB unavailable</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Next higher  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>No camera frames reach the device, so stock PCS messages are not forwarded to the car</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="005B6676"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">Local  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>R7 or R8 short ties camera CAN2_H to CAN2_L, so the camera bus is held recessive in intercept</t>
+          </r>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>HZ-011</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="30" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-023 · short
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Camera-side termination shorted in intercept</t>
+          </r>
+        </is>
+      </c>
+      <c r="G34" s="33" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="H34" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Termination resistor R7 or R8 short (FMEDA SG-009 FMD-036); pass-through is not affected (R7/R8 are on the NO side)</t>
+          </r>
+        </is>
+      </c>
+      <c r="I34" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• COTS comma 3X design in volume field use; no supplier reliability data, schematic or BOM available to LionDriver (WP-H-02 UK-01, UK-02)</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="005B6676"/>
+              <sz val="8"/>
+            </rPr>
+            <t xml:space="preserve">
+   assurance/04-hardware/WP-H-02-hardware-design.md</t>
+          </r>
+        </is>
+      </c>
+      <c r="J34" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="008A5A00"/>
+              <sz val="10"/>
+            </rPr>
+            <t>• No LionDriver hardware verification or qualification test exists for this cause; VS-HW-24 (e) checks the opens only (WP-H-06 v0.13)</t>
+          </r>
+        </is>
+      </c>
+      <c r="L34" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" s="37" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="N34" s="34" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="001F4E8C"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">DFM-ACT-014 · detection
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="001B2430"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+          </r>
+        </is>
+      </c>
+      <c r="O34" s="38" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="P34" s="33" t="inlineStr"/>
+      <c r="Q34" s="33" t="inlineStr"/>
+      <c r="R34" s="39" t="inlineStr"/>
+      <c r="S34" s="39" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:S32"/>
+  <autoFilter ref="A2:S34"/>
   <mergeCells count="46">
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="E5:E6"/>
@@ -8114,7 +8607,7 @@
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
+    <dataValidation sqref="R3 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this cause" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8122,7 +8615,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · rev 0.13 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8665,7 +9158,7 @@
       <c r="H14" s="53" t="inlineStr"/>
       <c r="I14" s="53" t="inlineStr"/>
     </row>
-    <row r="15" ht="100.5" customHeight="1">
+    <row r="15" ht="127.5" customHeight="1">
       <c r="A15" s="53" t="inlineStr">
         <is>
           <t>DFM-ACT-014</t>
@@ -8678,7 +9171,7 @@
       </c>
       <c r="C15" s="53" t="inlineStr">
         <is>
-          <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
+          <t>Bench-test the harness box failure behaviour (RR-2026-010): box unpowered with car and camera powered; R2/R3 forced open with the device silent; supply at 14-16 V against the DG419LE ratings; pass-through signal integrity; clamp-diode short on CAN0; camera-side termination R7/R8 lifted in intercept (VS-HW-24 (e), DFM-022); confirm the shipped box matches the v3 drawing (VS-HW-02). The decided route for the harness box (DQ-209 option A, 2026-10-16); procedures in WP-H-06 §3.1</t>
         </is>
       </c>
       <c r="D15" s="53" t="inlineStr">
@@ -8699,7 +9192,9 @@
 DFM-014.C2
 DFM-020.C1
 DFM-020.C2
-DFM-021.C1</t>
+DFM-021.C1
+DFM-022.C1
+DFM-023.C1</t>
         </is>
       </c>
       <c r="G15" s="53" t="inlineStr"/>
@@ -9101,7 +9596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10662,13 +11157,137 @@
       <c r="O25" s="49" t="inlineStr"/>
       <c r="P25" s="49" t="inlineStr"/>
     </row>
+    <row r="26" ht="100.5" customHeight="1">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>DFM-022 · Camera bus left unterminated in intercept</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>DFM-022.C1</t>
+        </is>
+      </c>
+      <c r="D26" s="44" t="inlineStr">
+        <is>
+          <t>Termination resistor R7 open together with R8 or the P13-P15 loopback open. One open alone leaves 120 ohm and a recessive edge of about 0.06 us, so it is latent (FMEDA SG-009 FMD-035); pass-through is not affected (R7/R8 are on the NO side)</t>
+        </is>
+      </c>
+      <c r="E26" s="44" t="inlineStr">
+        <is>
+          <t>None: the device checks only car-side messages for timeouts; a single open is latent and nothing checks the camera-side termination</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G26" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: stock PCS messages are lost while in intercept</t>
+        </is>
+      </c>
+      <c r="H26" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" s="55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L26" s="44" t="inlineStr"/>
+      <c r="M26" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N26" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr"/>
+      <c r="P26" s="49" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>DFM-023 · Camera-side termination shorted in intercept</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>DFM-023.C1</t>
+        </is>
+      </c>
+      <c r="D27" s="44" t="inlineStr">
+        <is>
+          <t>Termination resistor R7 or R8 short (FMEDA SG-009 FMD-036); pass-through is not affected (R7/R8 are on the NO side)</t>
+        </is>
+      </c>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>None: the device checks only car-side messages for timeouts, so a silent camera bus is not flagged</t>
+        </is>
+      </c>
+      <c r="F27" s="44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G27" s="44" t="inlineStr">
+        <is>
+          <t>Unchanged: stock PCS messages are lost while in intercept</t>
+        </is>
+      </c>
+      <c r="H27" s="45" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" s="47" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="L27" s="44" t="inlineStr"/>
+      <c r="M27" s="43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N27" s="44" t="inlineStr">
+        <is>
+          <t>DFM-ACT-014 · open</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr"/>
+      <c r="P27" s="49" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:P25"/>
+  <autoFilter ref="A2:P27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
+    <dataValidation sqref="O3 O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Review" prompt="Reviewer decision for this MSR row" type="list">
       <formula1>"Agree,Re-rate,Reject,Question"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10676,7 +11295,7 @@
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.12 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;LDFMEA — device, integrated panda, harness, vehicle interfaces · FMEA-MSR · rev 0.13 · BL-007&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
